--- a/endowment_pilas/data/DIVITIASSAS.xlsx
+++ b/endowment_pilas/data/DIVITIASSAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\navegasoft\divitas\endowment_employee\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorio\prueba_navegasoft\endowment_pilas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420F2C46-7A90-4B51-A947-A63F07E0CE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB49F22-09A9-44A0-976A-EFE21BC79714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="150" yWindow="90" windowWidth="18970" windowHeight="10060" firstSheet="1" activeTab="1" xr2:uid="{E1C59047-29BF-4165-B918-2314B64D924D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{E1C59047-29BF-4165-B918-2314B64D924D}"/>
   </bookViews>
   <sheets>
     <sheet name="DatosPruebaEmp" sheetId="2" state="veryHidden" r:id="rId1"/>
@@ -102,6 +102,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -7782,7 +7785,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,###"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7974,25 +7977,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -8004,6 +7992,21 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -8397,9 +8400,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62E8C2A8-6D5C-4176-8D33-3BE88C4C7400}">
   <dimension ref="A1:BW1106"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8422,7 +8425,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:75">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -8649,7 +8652,7 @@
         <v>2422</v>
       </c>
     </row>
-    <row r="4" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:75">
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
@@ -8870,7 +8873,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="5" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:75">
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
@@ -9061,7 +9064,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:75">
       <c r="C6" t="s">
         <v>12</v>
       </c>
@@ -9231,7 +9234,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="7" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:75">
       <c r="C7" t="s">
         <v>13</v>
       </c>
@@ -9386,7 +9389,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="8" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:75">
       <c r="C8" t="s">
         <v>14</v>
       </c>
@@ -9535,7 +9538,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="9" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:75">
       <c r="C9" t="s">
         <v>12</v>
       </c>
@@ -9669,7 +9672,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="10" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:75">
       <c r="D10" t="s">
         <v>22</v>
       </c>
@@ -9794,7 +9797,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="11" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:75">
       <c r="D11" t="s">
         <v>23</v>
       </c>
@@ -9919,7 +9922,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="12" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:75">
       <c r="D12" t="s">
         <v>24</v>
       </c>
@@ -10032,7 +10035,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="13" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:75">
       <c r="D13" t="s">
         <v>25</v>
       </c>
@@ -10145,7 +10148,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="14" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:75">
       <c r="D14" t="s">
         <v>26</v>
       </c>
@@ -10246,7 +10249,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="15" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:75">
       <c r="D15" t="s">
         <v>27</v>
       </c>
@@ -10344,7 +10347,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="16" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:75">
       <c r="D16" t="s">
         <v>28</v>
       </c>
@@ -10436,7 +10439,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="17" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="17" spans="6:71">
       <c r="F17" t="s">
         <v>52</v>
       </c>
@@ -10519,7 +10522,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="18" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="18" spans="6:71">
       <c r="F18" t="s">
         <v>53</v>
       </c>
@@ -10599,7 +10602,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="19" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="19" spans="6:71">
       <c r="F19" t="s">
         <v>54</v>
       </c>
@@ -10676,7 +10679,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="20" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="20" spans="6:71">
       <c r="F20" t="s">
         <v>55</v>
       </c>
@@ -10753,7 +10756,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="21" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="21" spans="6:71">
       <c r="F21" t="s">
         <v>56</v>
       </c>
@@ -10830,7 +10833,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="22" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="22" spans="6:71">
       <c r="F22" t="s">
         <v>57</v>
       </c>
@@ -10904,7 +10907,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="23" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="23" spans="6:71">
       <c r="F23" t="s">
         <v>58</v>
       </c>
@@ -10978,7 +10981,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="24" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="24" spans="6:71">
       <c r="F24" t="s">
         <v>59</v>
       </c>
@@ -11052,7 +11055,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="25" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="25" spans="6:71">
       <c r="F25" t="s">
         <v>60</v>
       </c>
@@ -11126,7 +11129,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="26" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="26" spans="6:71">
       <c r="F26" t="s">
         <v>61</v>
       </c>
@@ -11197,7 +11200,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="27" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="27" spans="6:71">
       <c r="F27" t="s">
         <v>62</v>
       </c>
@@ -11268,7 +11271,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="28" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="28" spans="6:71">
       <c r="F28" t="s">
         <v>63</v>
       </c>
@@ -11336,7 +11339,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="29" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="29" spans="6:71">
       <c r="F29" t="s">
         <v>64</v>
       </c>
@@ -11401,7 +11404,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="30" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="30" spans="6:71">
       <c r="F30" t="s">
         <v>65</v>
       </c>
@@ -11463,7 +11466,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="31" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="31" spans="6:71">
       <c r="F31" t="s">
         <v>66</v>
       </c>
@@ -11525,7 +11528,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="32" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="32" spans="6:71">
       <c r="F32" t="s">
         <v>67</v>
       </c>
@@ -11584,7 +11587,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="33" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="33" spans="6:71">
       <c r="F33" t="s">
         <v>68</v>
       </c>
@@ -11637,7 +11640,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="34" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="34" spans="6:71">
       <c r="F34" t="s">
         <v>69</v>
       </c>
@@ -11687,7 +11690,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="35" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="35" spans="6:71">
       <c r="F35" t="s">
         <v>70</v>
       </c>
@@ -11737,7 +11740,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="36" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="36" spans="6:71">
       <c r="F36" t="s">
         <v>71</v>
       </c>
@@ -11784,7 +11787,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="37" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="37" spans="6:71">
       <c r="F37" t="s">
         <v>72</v>
       </c>
@@ -11831,7 +11834,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="38" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="38" spans="6:71">
       <c r="F38" t="s">
         <v>73</v>
       </c>
@@ -11878,7 +11881,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="39" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="39" spans="6:71">
       <c r="F39" t="s">
         <v>74</v>
       </c>
@@ -11925,7 +11928,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="40" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="40" spans="6:71">
       <c r="J40" t="s">
         <v>137</v>
       </c>
@@ -11966,7 +11969,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="41" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="41" spans="6:71">
       <c r="J41" t="s">
         <v>138</v>
       </c>
@@ -12007,7 +12010,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="42" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="42" spans="6:71">
       <c r="J42" t="s">
         <v>139</v>
       </c>
@@ -12048,7 +12051,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="43" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="43" spans="6:71">
       <c r="J43" t="s">
         <v>140</v>
       </c>
@@ -12086,7 +12089,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="44" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="44" spans="6:71">
       <c r="J44" t="s">
         <v>141</v>
       </c>
@@ -12124,7 +12127,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="45" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="45" spans="6:71">
       <c r="J45" t="s">
         <v>142</v>
       </c>
@@ -12156,7 +12159,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="46" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="46" spans="6:71">
       <c r="J46" t="s">
         <v>143</v>
       </c>
@@ -12185,7 +12188,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="47" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="47" spans="6:71">
       <c r="J47" t="s">
         <v>144</v>
       </c>
@@ -12214,7 +12217,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="48" spans="6:71" x14ac:dyDescent="0.35">
+    <row r="48" spans="6:71">
       <c r="J48" t="s">
         <v>145</v>
       </c>
@@ -12243,7 +12246,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="49" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="49" spans="10:71">
       <c r="J49" t="s">
         <v>146</v>
       </c>
@@ -12269,7 +12272,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="50" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="50" spans="10:71">
       <c r="AG50" t="s">
         <v>333</v>
       </c>
@@ -12289,7 +12292,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="51" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="51" spans="10:71">
       <c r="AG51" t="s">
         <v>334</v>
       </c>
@@ -12309,7 +12312,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="52" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="52" spans="10:71">
       <c r="AG52" t="s">
         <v>335</v>
       </c>
@@ -12329,7 +12332,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="53" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="53" spans="10:71">
       <c r="AG53" t="s">
         <v>336</v>
       </c>
@@ -12349,7 +12352,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="54" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="54" spans="10:71">
       <c r="AG54" t="s">
         <v>337</v>
       </c>
@@ -12369,7 +12372,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="55" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="55" spans="10:71">
       <c r="AG55" t="s">
         <v>338</v>
       </c>
@@ -12389,7 +12392,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="56" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="56" spans="10:71">
       <c r="AG56" t="s">
         <v>339</v>
       </c>
@@ -12409,7 +12412,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="57" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="57" spans="10:71">
       <c r="AG57" t="s">
         <v>340</v>
       </c>
@@ -12429,7 +12432,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="58" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="58" spans="10:71">
       <c r="AG58" t="s">
         <v>341</v>
       </c>
@@ -12449,7 +12452,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="59" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="59" spans="10:71">
       <c r="AG59" t="s">
         <v>342</v>
       </c>
@@ -12469,7 +12472,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="60" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="60" spans="10:71">
       <c r="AG60" t="s">
         <v>343</v>
       </c>
@@ -12489,7 +12492,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="61" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="61" spans="10:71">
       <c r="AG61" t="s">
         <v>344</v>
       </c>
@@ -12509,7 +12512,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="62" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="62" spans="10:71">
       <c r="AG62" t="s">
         <v>345</v>
       </c>
@@ -12529,7 +12532,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="63" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="63" spans="10:71">
       <c r="AG63" t="s">
         <v>346</v>
       </c>
@@ -12549,7 +12552,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="64" spans="10:71" x14ac:dyDescent="0.35">
+    <row r="64" spans="10:71">
       <c r="AG64" t="s">
         <v>347</v>
       </c>
@@ -12569,7 +12572,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="65" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="65" spans="33:71">
       <c r="AG65" t="s">
         <v>348</v>
       </c>
@@ -12589,7 +12592,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="66" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="66" spans="33:71">
       <c r="AG66" t="s">
         <v>349</v>
       </c>
@@ -12609,7 +12612,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="67" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="67" spans="33:71">
       <c r="AG67" t="s">
         <v>350</v>
       </c>
@@ -12626,7 +12629,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="68" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="68" spans="33:71">
       <c r="AG68" t="s">
         <v>351</v>
       </c>
@@ -12643,7 +12646,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="69" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="69" spans="33:71">
       <c r="AG69" t="s">
         <v>352</v>
       </c>
@@ -12660,7 +12663,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="70" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="70" spans="33:71">
       <c r="AG70" t="s">
         <v>353</v>
       </c>
@@ -12677,7 +12680,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="71" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="71" spans="33:71">
       <c r="AG71" t="s">
         <v>354</v>
       </c>
@@ -12694,7 +12697,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="72" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="72" spans="33:71">
       <c r="AG72" t="s">
         <v>355</v>
       </c>
@@ -12711,7 +12714,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="73" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="73" spans="33:71">
       <c r="AG73" t="s">
         <v>356</v>
       </c>
@@ -12728,7 +12731,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="74" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="74" spans="33:71">
       <c r="AG74" t="s">
         <v>357</v>
       </c>
@@ -12745,7 +12748,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="75" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="75" spans="33:71">
       <c r="AG75" t="s">
         <v>264</v>
       </c>
@@ -12762,7 +12765,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="76" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="76" spans="33:71">
       <c r="AG76" t="s">
         <v>358</v>
       </c>
@@ -12779,7 +12782,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="77" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="77" spans="33:71">
       <c r="AG77" t="s">
         <v>359</v>
       </c>
@@ -12796,7 +12799,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="78" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="78" spans="33:71">
       <c r="AG78" t="s">
         <v>360</v>
       </c>
@@ -12813,7 +12816,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="79" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="79" spans="33:71">
       <c r="AG79" t="s">
         <v>361</v>
       </c>
@@ -12830,7 +12833,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="80" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="80" spans="33:71">
       <c r="AG80" t="s">
         <v>362</v>
       </c>
@@ -12847,7 +12850,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="81" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="81" spans="33:71">
       <c r="AG81" t="s">
         <v>363</v>
       </c>
@@ -12864,7 +12867,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="82" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="82" spans="33:71">
       <c r="AG82" t="s">
         <v>364</v>
       </c>
@@ -12881,7 +12884,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="83" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="83" spans="33:71">
       <c r="AG83" t="s">
         <v>365</v>
       </c>
@@ -12898,7 +12901,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="84" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="84" spans="33:71">
       <c r="AG84" t="s">
         <v>366</v>
       </c>
@@ -12915,7 +12918,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="85" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="85" spans="33:71">
       <c r="AG85" t="s">
         <v>367</v>
       </c>
@@ -12932,7 +12935,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="86" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="86" spans="33:71">
       <c r="AG86" t="s">
         <v>368</v>
       </c>
@@ -12949,7 +12952,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="87" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="87" spans="33:71">
       <c r="AG87" t="s">
         <v>369</v>
       </c>
@@ -12966,7 +12969,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="88" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="88" spans="33:71">
       <c r="AG88" t="s">
         <v>370</v>
       </c>
@@ -12983,7 +12986,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="89" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="89" spans="33:71">
       <c r="AG89" t="s">
         <v>371</v>
       </c>
@@ -13000,7 +13003,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="90" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="90" spans="33:71">
       <c r="AG90" t="s">
         <v>372</v>
       </c>
@@ -13014,7 +13017,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="91" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="91" spans="33:71">
       <c r="AG91" t="s">
         <v>373</v>
       </c>
@@ -13028,7 +13031,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="92" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="92" spans="33:71">
       <c r="AG92" t="s">
         <v>374</v>
       </c>
@@ -13042,7 +13045,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="93" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="93" spans="33:71">
       <c r="AG93" t="s">
         <v>375</v>
       </c>
@@ -13056,7 +13059,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="94" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="94" spans="33:71">
       <c r="AG94" t="s">
         <v>376</v>
       </c>
@@ -13070,7 +13073,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="95" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="95" spans="33:71">
       <c r="AG95" t="s">
         <v>377</v>
       </c>
@@ -13084,7 +13087,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="96" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="96" spans="33:71">
       <c r="AG96" t="s">
         <v>378</v>
       </c>
@@ -13098,7 +13101,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="97" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="97" spans="33:71">
       <c r="AG97" t="s">
         <v>379</v>
       </c>
@@ -13112,7 +13115,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="98" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="98" spans="33:71">
       <c r="AG98" t="s">
         <v>380</v>
       </c>
@@ -13126,7 +13129,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="99" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="99" spans="33:71">
       <c r="AG99" t="s">
         <v>381</v>
       </c>
@@ -13140,7 +13143,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="100" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="100" spans="33:71">
       <c r="AG100" t="s">
         <v>382</v>
       </c>
@@ -13154,7 +13157,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="101" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="101" spans="33:71">
       <c r="AG101" t="s">
         <v>383</v>
       </c>
@@ -13168,7 +13171,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="102" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="102" spans="33:71">
       <c r="AG102" t="s">
         <v>384</v>
       </c>
@@ -13182,7 +13185,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="103" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="103" spans="33:71">
       <c r="AG103" t="s">
         <v>385</v>
       </c>
@@ -13196,7 +13199,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="104" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="104" spans="33:71">
       <c r="AG104" t="s">
         <v>386</v>
       </c>
@@ -13210,7 +13213,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="105" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="105" spans="33:71">
       <c r="AG105" t="s">
         <v>387</v>
       </c>
@@ -13224,7 +13227,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="106" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="106" spans="33:71">
       <c r="AG106" t="s">
         <v>388</v>
       </c>
@@ -13238,7 +13241,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="107" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="107" spans="33:71">
       <c r="AG107" t="s">
         <v>389</v>
       </c>
@@ -13252,7 +13255,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="108" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="108" spans="33:71">
       <c r="AG108" t="s">
         <v>390</v>
       </c>
@@ -13266,7 +13269,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="109" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="109" spans="33:71">
       <c r="AG109" t="s">
         <v>391</v>
       </c>
@@ -13280,7 +13283,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="110" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="110" spans="33:71">
       <c r="AG110" t="s">
         <v>392</v>
       </c>
@@ -13294,7 +13297,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="111" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="111" spans="33:71">
       <c r="AG111" t="s">
         <v>393</v>
       </c>
@@ -13308,7 +13311,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="112" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="112" spans="33:71">
       <c r="AG112" t="s">
         <v>394</v>
       </c>
@@ -13322,7 +13325,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="113" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="113" spans="33:71">
       <c r="AG113" t="s">
         <v>395</v>
       </c>
@@ -13336,7 +13339,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="114" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="114" spans="33:71">
       <c r="AG114" t="s">
         <v>396</v>
       </c>
@@ -13350,7 +13353,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="115" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="115" spans="33:71">
       <c r="AG115" t="s">
         <v>397</v>
       </c>
@@ -13364,7 +13367,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="116" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="116" spans="33:71">
       <c r="AG116" t="s">
         <v>398</v>
       </c>
@@ -13378,7 +13381,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="117" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="117" spans="33:71">
       <c r="AG117" t="s">
         <v>399</v>
       </c>
@@ -13392,7 +13395,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="118" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="118" spans="33:71">
       <c r="AG118" t="s">
         <v>400</v>
       </c>
@@ -13406,7 +13409,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="119" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="119" spans="33:71">
       <c r="AG119" t="s">
         <v>401</v>
       </c>
@@ -13417,7 +13420,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="120" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="120" spans="33:71">
       <c r="AG120" t="s">
         <v>402</v>
       </c>
@@ -13428,7 +13431,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="121" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="121" spans="33:71">
       <c r="AG121" t="s">
         <v>403</v>
       </c>
@@ -13439,7 +13442,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="122" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="122" spans="33:71">
       <c r="AG122" t="s">
         <v>404</v>
       </c>
@@ -13450,7 +13453,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="123" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="123" spans="33:71">
       <c r="AG123" t="s">
         <v>405</v>
       </c>
@@ -13461,7 +13464,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="124" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="124" spans="33:71">
       <c r="AG124" t="s">
         <v>406</v>
       </c>
@@ -13472,7 +13475,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="125" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="125" spans="33:71">
       <c r="AG125" t="s">
         <v>407</v>
       </c>
@@ -13483,7 +13486,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="126" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="126" spans="33:71">
       <c r="AG126" t="s">
         <v>408</v>
       </c>
@@ -13491,7 +13494,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="127" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="127" spans="33:71">
       <c r="AG127" t="s">
         <v>409</v>
       </c>
@@ -13499,4897 +13502,4897 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="128" spans="33:71" x14ac:dyDescent="0.35">
+    <row r="128" spans="33:71">
       <c r="BS128" s="1" t="s">
         <v>1441</v>
       </c>
     </row>
-    <row r="129" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="129" spans="71:71">
       <c r="BS129" s="1" t="s">
         <v>1442</v>
       </c>
     </row>
-    <row r="130" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="130" spans="71:71">
       <c r="BS130" s="1" t="s">
         <v>1443</v>
       </c>
     </row>
-    <row r="131" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="131" spans="71:71">
       <c r="BS131" s="1" t="s">
         <v>1444</v>
       </c>
     </row>
-    <row r="132" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="132" spans="71:71">
       <c r="BS132" s="1" t="s">
         <v>1445</v>
       </c>
     </row>
-    <row r="133" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="133" spans="71:71">
       <c r="BS133" s="1" t="s">
         <v>1446</v>
       </c>
     </row>
-    <row r="134" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="134" spans="71:71">
       <c r="BS134" s="1" t="s">
         <v>1447</v>
       </c>
     </row>
-    <row r="135" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="135" spans="71:71">
       <c r="BS135" s="1" t="s">
         <v>1448</v>
       </c>
     </row>
-    <row r="136" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="136" spans="71:71">
       <c r="BS136" s="1" t="s">
         <v>1449</v>
       </c>
     </row>
-    <row r="137" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="137" spans="71:71">
       <c r="BS137" s="1" t="s">
         <v>1450</v>
       </c>
     </row>
-    <row r="138" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="138" spans="71:71">
       <c r="BS138" s="1" t="s">
         <v>1451</v>
       </c>
     </row>
-    <row r="139" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="139" spans="71:71">
       <c r="BS139" s="1" t="s">
         <v>1452</v>
       </c>
     </row>
-    <row r="140" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="140" spans="71:71">
       <c r="BS140" s="1" t="s">
         <v>1453</v>
       </c>
     </row>
-    <row r="141" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="141" spans="71:71">
       <c r="BS141" s="1" t="s">
         <v>1454</v>
       </c>
     </row>
-    <row r="142" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="142" spans="71:71">
       <c r="BS142" s="1" t="s">
         <v>1455</v>
       </c>
     </row>
-    <row r="143" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="143" spans="71:71">
       <c r="BS143" s="1" t="s">
         <v>1456</v>
       </c>
     </row>
-    <row r="144" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="144" spans="71:71">
       <c r="BS144" s="1" t="s">
         <v>1457</v>
       </c>
     </row>
-    <row r="145" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="145" spans="71:71">
       <c r="BS145" s="1" t="s">
         <v>1458</v>
       </c>
     </row>
-    <row r="146" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="146" spans="71:71">
       <c r="BS146" s="1" t="s">
         <v>1459</v>
       </c>
     </row>
-    <row r="147" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="147" spans="71:71">
       <c r="BS147" s="1" t="s">
         <v>1460</v>
       </c>
     </row>
-    <row r="148" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="148" spans="71:71">
       <c r="BS148" s="1" t="s">
         <v>1461</v>
       </c>
     </row>
-    <row r="149" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="149" spans="71:71">
       <c r="BS149" s="1" t="s">
         <v>1462</v>
       </c>
     </row>
-    <row r="150" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="150" spans="71:71">
       <c r="BS150" s="1" t="s">
         <v>1463</v>
       </c>
     </row>
-    <row r="151" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="151" spans="71:71">
       <c r="BS151" s="1" t="s">
         <v>1464</v>
       </c>
     </row>
-    <row r="152" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="152" spans="71:71">
       <c r="BS152" s="1" t="s">
         <v>1465</v>
       </c>
     </row>
-    <row r="153" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="153" spans="71:71">
       <c r="BS153" s="1" t="s">
         <v>1466</v>
       </c>
     </row>
-    <row r="154" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="154" spans="71:71">
       <c r="BS154" s="1" t="s">
         <v>1467</v>
       </c>
     </row>
-    <row r="155" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="155" spans="71:71">
       <c r="BS155" s="1" t="s">
         <v>1468</v>
       </c>
     </row>
-    <row r="156" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="156" spans="71:71">
       <c r="BS156" s="1" t="s">
         <v>1469</v>
       </c>
     </row>
-    <row r="157" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="157" spans="71:71">
       <c r="BS157" s="1" t="s">
         <v>1470</v>
       </c>
     </row>
-    <row r="158" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="158" spans="71:71">
       <c r="BS158" s="1" t="s">
         <v>1471</v>
       </c>
     </row>
-    <row r="159" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="159" spans="71:71">
       <c r="BS159" s="1" t="s">
         <v>1472</v>
       </c>
     </row>
-    <row r="160" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="160" spans="71:71">
       <c r="BS160" s="1" t="s">
         <v>1473</v>
       </c>
     </row>
-    <row r="161" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="161" spans="71:71">
       <c r="BS161" s="1" t="s">
         <v>1474</v>
       </c>
     </row>
-    <row r="162" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="162" spans="71:71">
       <c r="BS162" s="1" t="s">
         <v>1475</v>
       </c>
     </row>
-    <row r="163" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="163" spans="71:71">
       <c r="BS163" s="1" t="s">
         <v>1476</v>
       </c>
     </row>
-    <row r="164" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="164" spans="71:71">
       <c r="BS164" s="1" t="s">
         <v>1477</v>
       </c>
     </row>
-    <row r="165" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="165" spans="71:71">
       <c r="BS165" s="1" t="s">
         <v>1478</v>
       </c>
     </row>
-    <row r="166" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="166" spans="71:71">
       <c r="BS166" s="1" t="s">
         <v>1479</v>
       </c>
     </row>
-    <row r="167" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="167" spans="71:71">
       <c r="BS167" s="1" t="s">
         <v>1480</v>
       </c>
     </row>
-    <row r="168" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="168" spans="71:71">
       <c r="BS168" s="1" t="s">
         <v>1481</v>
       </c>
     </row>
-    <row r="169" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="169" spans="71:71">
       <c r="BS169" s="1" t="s">
         <v>1482</v>
       </c>
     </row>
-    <row r="170" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="170" spans="71:71">
       <c r="BS170" s="1" t="s">
         <v>1483</v>
       </c>
     </row>
-    <row r="171" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="171" spans="71:71">
       <c r="BS171" s="1" t="s">
         <v>1484</v>
       </c>
     </row>
-    <row r="172" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="172" spans="71:71">
       <c r="BS172" s="1" t="s">
         <v>1485</v>
       </c>
     </row>
-    <row r="173" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="173" spans="71:71">
       <c r="BS173" s="1" t="s">
         <v>1486</v>
       </c>
     </row>
-    <row r="174" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="174" spans="71:71">
       <c r="BS174" s="1" t="s">
         <v>1487</v>
       </c>
     </row>
-    <row r="175" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="175" spans="71:71">
       <c r="BS175" s="1" t="s">
         <v>1488</v>
       </c>
     </row>
-    <row r="176" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="176" spans="71:71">
       <c r="BS176" s="1" t="s">
         <v>1489</v>
       </c>
     </row>
-    <row r="177" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="177" spans="71:71">
       <c r="BS177" s="1" t="s">
         <v>1490</v>
       </c>
     </row>
-    <row r="178" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="178" spans="71:71">
       <c r="BS178" s="1" t="s">
         <v>1491</v>
       </c>
     </row>
-    <row r="179" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="179" spans="71:71">
       <c r="BS179" s="1" t="s">
         <v>1492</v>
       </c>
     </row>
-    <row r="180" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="180" spans="71:71">
       <c r="BS180" s="1" t="s">
         <v>1493</v>
       </c>
     </row>
-    <row r="181" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="181" spans="71:71">
       <c r="BS181" s="1" t="s">
         <v>1494</v>
       </c>
     </row>
-    <row r="182" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="182" spans="71:71">
       <c r="BS182" s="1" t="s">
         <v>1495</v>
       </c>
     </row>
-    <row r="183" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="183" spans="71:71">
       <c r="BS183" s="1" t="s">
         <v>1496</v>
       </c>
     </row>
-    <row r="184" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="184" spans="71:71">
       <c r="BS184" s="1" t="s">
         <v>1497</v>
       </c>
     </row>
-    <row r="185" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="185" spans="71:71">
       <c r="BS185" s="1" t="s">
         <v>1498</v>
       </c>
     </row>
-    <row r="186" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="186" spans="71:71">
       <c r="BS186" s="1" t="s">
         <v>1499</v>
       </c>
     </row>
-    <row r="187" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="187" spans="71:71">
       <c r="BS187" s="1" t="s">
         <v>1500</v>
       </c>
     </row>
-    <row r="188" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="188" spans="71:71">
       <c r="BS188" s="1" t="s">
         <v>1501</v>
       </c>
     </row>
-    <row r="189" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="189" spans="71:71">
       <c r="BS189" s="1" t="s">
         <v>1502</v>
       </c>
     </row>
-    <row r="190" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="190" spans="71:71">
       <c r="BS190" s="1" t="s">
         <v>1503</v>
       </c>
     </row>
-    <row r="191" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="191" spans="71:71">
       <c r="BS191" s="1" t="s">
         <v>1504</v>
       </c>
     </row>
-    <row r="192" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="192" spans="71:71">
       <c r="BS192" s="1" t="s">
         <v>1505</v>
       </c>
     </row>
-    <row r="193" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="193" spans="71:71">
       <c r="BS193" s="1" t="s">
         <v>1506</v>
       </c>
     </row>
-    <row r="194" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="194" spans="71:71">
       <c r="BS194" s="1" t="s">
         <v>1507</v>
       </c>
     </row>
-    <row r="195" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="195" spans="71:71">
       <c r="BS195" s="1" t="s">
         <v>1508</v>
       </c>
     </row>
-    <row r="196" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="196" spans="71:71">
       <c r="BS196" s="1" t="s">
         <v>1509</v>
       </c>
     </row>
-    <row r="197" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="197" spans="71:71">
       <c r="BS197" s="1" t="s">
         <v>1510</v>
       </c>
     </row>
-    <row r="198" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="198" spans="71:71">
       <c r="BS198" s="1" t="s">
         <v>1511</v>
       </c>
     </row>
-    <row r="199" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="199" spans="71:71">
       <c r="BS199" s="1" t="s">
         <v>1512</v>
       </c>
     </row>
-    <row r="200" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="200" spans="71:71">
       <c r="BS200" s="1" t="s">
         <v>1513</v>
       </c>
     </row>
-    <row r="201" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="201" spans="71:71">
       <c r="BS201" s="1" t="s">
         <v>1514</v>
       </c>
     </row>
-    <row r="202" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="202" spans="71:71">
       <c r="BS202" s="1" t="s">
         <v>1515</v>
       </c>
     </row>
-    <row r="203" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="203" spans="71:71">
       <c r="BS203" s="1" t="s">
         <v>1516</v>
       </c>
     </row>
-    <row r="204" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="204" spans="71:71">
       <c r="BS204" s="1" t="s">
         <v>1517</v>
       </c>
     </row>
-    <row r="205" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="205" spans="71:71">
       <c r="BS205" s="1" t="s">
         <v>1518</v>
       </c>
     </row>
-    <row r="206" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="206" spans="71:71">
       <c r="BS206" s="1" t="s">
         <v>1519</v>
       </c>
     </row>
-    <row r="207" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="207" spans="71:71">
       <c r="BS207" s="1" t="s">
         <v>1520</v>
       </c>
     </row>
-    <row r="208" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="208" spans="71:71">
       <c r="BS208" s="1" t="s">
         <v>1521</v>
       </c>
     </row>
-    <row r="209" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="209" spans="71:71">
       <c r="BS209" s="1" t="s">
         <v>1522</v>
       </c>
     </row>
-    <row r="210" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="210" spans="71:71">
       <c r="BS210" s="1" t="s">
         <v>1523</v>
       </c>
     </row>
-    <row r="211" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="211" spans="71:71">
       <c r="BS211" s="1" t="s">
         <v>1524</v>
       </c>
     </row>
-    <row r="212" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="212" spans="71:71">
       <c r="BS212" s="1" t="s">
         <v>1525</v>
       </c>
     </row>
-    <row r="213" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="213" spans="71:71">
       <c r="BS213" s="1" t="s">
         <v>1526</v>
       </c>
     </row>
-    <row r="214" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="214" spans="71:71">
       <c r="BS214" s="1" t="s">
         <v>1527</v>
       </c>
     </row>
-    <row r="215" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="215" spans="71:71">
       <c r="BS215" s="1" t="s">
         <v>1528</v>
       </c>
     </row>
-    <row r="216" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="216" spans="71:71">
       <c r="BS216" s="1" t="s">
         <v>1529</v>
       </c>
     </row>
-    <row r="217" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="217" spans="71:71">
       <c r="BS217" s="1" t="s">
         <v>1530</v>
       </c>
     </row>
-    <row r="218" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="218" spans="71:71">
       <c r="BS218" s="1" t="s">
         <v>1531</v>
       </c>
     </row>
-    <row r="219" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="219" spans="71:71">
       <c r="BS219" s="1" t="s">
         <v>1532</v>
       </c>
     </row>
-    <row r="220" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="220" spans="71:71">
       <c r="BS220" s="1" t="s">
         <v>1533</v>
       </c>
     </row>
-    <row r="221" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="221" spans="71:71">
       <c r="BS221" s="1" t="s">
         <v>1534</v>
       </c>
     </row>
-    <row r="222" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="222" spans="71:71">
       <c r="BS222" s="1" t="s">
         <v>1535</v>
       </c>
     </row>
-    <row r="223" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="223" spans="71:71">
       <c r="BS223" s="1" t="s">
         <v>1536</v>
       </c>
     </row>
-    <row r="224" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="224" spans="71:71">
       <c r="BS224" s="1" t="s">
         <v>1537</v>
       </c>
     </row>
-    <row r="225" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="225" spans="71:71">
       <c r="BS225" s="1" t="s">
         <v>1538</v>
       </c>
     </row>
-    <row r="226" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="226" spans="71:71">
       <c r="BS226" s="1" t="s">
         <v>1539</v>
       </c>
     </row>
-    <row r="227" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="227" spans="71:71">
       <c r="BS227" s="1" t="s">
         <v>1540</v>
       </c>
     </row>
-    <row r="228" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="228" spans="71:71">
       <c r="BS228" s="1" t="s">
         <v>1541</v>
       </c>
     </row>
-    <row r="229" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="229" spans="71:71">
       <c r="BS229" s="1" t="s">
         <v>1542</v>
       </c>
     </row>
-    <row r="230" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="230" spans="71:71">
       <c r="BS230" s="1" t="s">
         <v>1543</v>
       </c>
     </row>
-    <row r="231" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="231" spans="71:71">
       <c r="BS231" s="1" t="s">
         <v>1544</v>
       </c>
     </row>
-    <row r="232" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="232" spans="71:71">
       <c r="BS232" s="1" t="s">
         <v>1545</v>
       </c>
     </row>
-    <row r="233" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="233" spans="71:71">
       <c r="BS233" s="1" t="s">
         <v>1546</v>
       </c>
     </row>
-    <row r="234" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="234" spans="71:71">
       <c r="BS234" s="1" t="s">
         <v>1547</v>
       </c>
     </row>
-    <row r="235" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="235" spans="71:71">
       <c r="BS235" s="1" t="s">
         <v>1548</v>
       </c>
     </row>
-    <row r="236" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="236" spans="71:71">
       <c r="BS236" s="1" t="s">
         <v>1549</v>
       </c>
     </row>
-    <row r="237" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="237" spans="71:71">
       <c r="BS237" s="1" t="s">
         <v>1550</v>
       </c>
     </row>
-    <row r="238" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="238" spans="71:71">
       <c r="BS238" s="1" t="s">
         <v>1551</v>
       </c>
     </row>
-    <row r="239" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="239" spans="71:71">
       <c r="BS239" s="1" t="s">
         <v>1552</v>
       </c>
     </row>
-    <row r="240" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="240" spans="71:71">
       <c r="BS240" s="1" t="s">
         <v>1553</v>
       </c>
     </row>
-    <row r="241" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="241" spans="71:71">
       <c r="BS241" s="1" t="s">
         <v>1554</v>
       </c>
     </row>
-    <row r="242" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="242" spans="71:71">
       <c r="BS242" s="1" t="s">
         <v>1555</v>
       </c>
     </row>
-    <row r="243" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="243" spans="71:71">
       <c r="BS243" s="1" t="s">
         <v>1556</v>
       </c>
     </row>
-    <row r="244" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="244" spans="71:71">
       <c r="BS244" s="1" t="s">
         <v>1557</v>
       </c>
     </row>
-    <row r="245" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="245" spans="71:71">
       <c r="BS245" s="1" t="s">
         <v>1558</v>
       </c>
     </row>
-    <row r="246" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="246" spans="71:71">
       <c r="BS246" s="1" t="s">
         <v>1559</v>
       </c>
     </row>
-    <row r="247" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="247" spans="71:71">
       <c r="BS247" s="1" t="s">
         <v>1560</v>
       </c>
     </row>
-    <row r="248" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="248" spans="71:71">
       <c r="BS248" s="1" t="s">
         <v>1561</v>
       </c>
     </row>
-    <row r="249" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="249" spans="71:71">
       <c r="BS249" s="1" t="s">
         <v>1562</v>
       </c>
     </row>
-    <row r="250" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="250" spans="71:71">
       <c r="BS250" s="1" t="s">
         <v>1563</v>
       </c>
     </row>
-    <row r="251" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="251" spans="71:71">
       <c r="BS251" s="1" t="s">
         <v>1564</v>
       </c>
     </row>
-    <row r="252" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="252" spans="71:71">
       <c r="BS252" s="1" t="s">
         <v>1565</v>
       </c>
     </row>
-    <row r="253" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="253" spans="71:71">
       <c r="BS253" s="1" t="s">
         <v>1566</v>
       </c>
     </row>
-    <row r="254" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="254" spans="71:71">
       <c r="BS254" s="1" t="s">
         <v>1567</v>
       </c>
     </row>
-    <row r="255" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="255" spans="71:71">
       <c r="BS255" s="1" t="s">
         <v>1568</v>
       </c>
     </row>
-    <row r="256" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="256" spans="71:71">
       <c r="BS256" s="1" t="s">
         <v>1569</v>
       </c>
     </row>
-    <row r="257" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="257" spans="71:71">
       <c r="BS257" s="1" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="258" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="258" spans="71:71">
       <c r="BS258" s="1" t="s">
         <v>1571</v>
       </c>
     </row>
-    <row r="259" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="259" spans="71:71">
       <c r="BS259" s="1" t="s">
         <v>1572</v>
       </c>
     </row>
-    <row r="260" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="260" spans="71:71">
       <c r="BS260" s="1" t="s">
         <v>1573</v>
       </c>
     </row>
-    <row r="261" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="261" spans="71:71">
       <c r="BS261" s="1" t="s">
         <v>1574</v>
       </c>
     </row>
-    <row r="262" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="262" spans="71:71">
       <c r="BS262" s="1" t="s">
         <v>1575</v>
       </c>
     </row>
-    <row r="263" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="263" spans="71:71">
       <c r="BS263" s="1" t="s">
         <v>1576</v>
       </c>
     </row>
-    <row r="264" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="264" spans="71:71">
       <c r="BS264" s="1" t="s">
         <v>1577</v>
       </c>
     </row>
-    <row r="265" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="265" spans="71:71">
       <c r="BS265" s="1" t="s">
         <v>1578</v>
       </c>
     </row>
-    <row r="266" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="266" spans="71:71">
       <c r="BS266" s="1" t="s">
         <v>1579</v>
       </c>
     </row>
-    <row r="267" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="267" spans="71:71">
       <c r="BS267" s="1" t="s">
         <v>1580</v>
       </c>
     </row>
-    <row r="268" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="268" spans="71:71">
       <c r="BS268" s="1" t="s">
         <v>1581</v>
       </c>
     </row>
-    <row r="269" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="269" spans="71:71">
       <c r="BS269" s="1" t="s">
         <v>1582</v>
       </c>
     </row>
-    <row r="270" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="270" spans="71:71">
       <c r="BS270" s="1" t="s">
         <v>1583</v>
       </c>
     </row>
-    <row r="271" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="271" spans="71:71">
       <c r="BS271" s="1" t="s">
         <v>1584</v>
       </c>
     </row>
-    <row r="272" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="272" spans="71:71">
       <c r="BS272" s="1" t="s">
         <v>1585</v>
       </c>
     </row>
-    <row r="273" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="273" spans="71:71">
       <c r="BS273" s="1" t="s">
         <v>1586</v>
       </c>
     </row>
-    <row r="274" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="274" spans="71:71">
       <c r="BS274" s="1" t="s">
         <v>1587</v>
       </c>
     </row>
-    <row r="275" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="275" spans="71:71">
       <c r="BS275" s="1" t="s">
         <v>1588</v>
       </c>
     </row>
-    <row r="276" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="276" spans="71:71">
       <c r="BS276" s="1" t="s">
         <v>1589</v>
       </c>
     </row>
-    <row r="277" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="277" spans="71:71">
       <c r="BS277" s="1" t="s">
         <v>1590</v>
       </c>
     </row>
-    <row r="278" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="278" spans="71:71">
       <c r="BS278" s="1" t="s">
         <v>1591</v>
       </c>
     </row>
-    <row r="279" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="279" spans="71:71">
       <c r="BS279" s="1" t="s">
         <v>1592</v>
       </c>
     </row>
-    <row r="280" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="280" spans="71:71">
       <c r="BS280" s="1" t="s">
         <v>1593</v>
       </c>
     </row>
-    <row r="281" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="281" spans="71:71">
       <c r="BS281" s="1" t="s">
         <v>1594</v>
       </c>
     </row>
-    <row r="282" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="282" spans="71:71">
       <c r="BS282" s="1" t="s">
         <v>1595</v>
       </c>
     </row>
-    <row r="283" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="283" spans="71:71">
       <c r="BS283" s="1" t="s">
         <v>1596</v>
       </c>
     </row>
-    <row r="284" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="284" spans="71:71">
       <c r="BS284" s="1" t="s">
         <v>1597</v>
       </c>
     </row>
-    <row r="285" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="285" spans="71:71">
       <c r="BS285" s="1" t="s">
         <v>1598</v>
       </c>
     </row>
-    <row r="286" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="286" spans="71:71">
       <c r="BS286" s="1" t="s">
         <v>1599</v>
       </c>
     </row>
-    <row r="287" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="287" spans="71:71">
       <c r="BS287" s="1" t="s">
         <v>1600</v>
       </c>
     </row>
-    <row r="288" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="288" spans="71:71">
       <c r="BS288" s="1" t="s">
         <v>1601</v>
       </c>
     </row>
-    <row r="289" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="289" spans="71:71">
       <c r="BS289" s="1" t="s">
         <v>1602</v>
       </c>
     </row>
-    <row r="290" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="290" spans="71:71">
       <c r="BS290" s="1" t="s">
         <v>1603</v>
       </c>
     </row>
-    <row r="291" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="291" spans="71:71">
       <c r="BS291" s="1" t="s">
         <v>1604</v>
       </c>
     </row>
-    <row r="292" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="292" spans="71:71">
       <c r="BS292" s="1" t="s">
         <v>1605</v>
       </c>
     </row>
-    <row r="293" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="293" spans="71:71">
       <c r="BS293" s="1" t="s">
         <v>1606</v>
       </c>
     </row>
-    <row r="294" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="294" spans="71:71">
       <c r="BS294" s="1" t="s">
         <v>1607</v>
       </c>
     </row>
-    <row r="295" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="295" spans="71:71">
       <c r="BS295" s="1" t="s">
         <v>1608</v>
       </c>
     </row>
-    <row r="296" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="296" spans="71:71">
       <c r="BS296" s="1" t="s">
         <v>1609</v>
       </c>
     </row>
-    <row r="297" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="297" spans="71:71">
       <c r="BS297" s="1" t="s">
         <v>1610</v>
       </c>
     </row>
-    <row r="298" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="298" spans="71:71">
       <c r="BS298" s="1" t="s">
         <v>1611</v>
       </c>
     </row>
-    <row r="299" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="299" spans="71:71">
       <c r="BS299" s="1" t="s">
         <v>1612</v>
       </c>
     </row>
-    <row r="300" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="300" spans="71:71">
       <c r="BS300" s="1" t="s">
         <v>1613</v>
       </c>
     </row>
-    <row r="301" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="301" spans="71:71">
       <c r="BS301" s="1" t="s">
         <v>1614</v>
       </c>
     </row>
-    <row r="302" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="302" spans="71:71">
       <c r="BS302" s="1" t="s">
         <v>1615</v>
       </c>
     </row>
-    <row r="303" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="303" spans="71:71">
       <c r="BS303" s="1" t="s">
         <v>1616</v>
       </c>
     </row>
-    <row r="304" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="304" spans="71:71">
       <c r="BS304" s="1" t="s">
         <v>1617</v>
       </c>
     </row>
-    <row r="305" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="305" spans="71:71">
       <c r="BS305" s="1" t="s">
         <v>1618</v>
       </c>
     </row>
-    <row r="306" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="306" spans="71:71">
       <c r="BS306" s="1" t="s">
         <v>1619</v>
       </c>
     </row>
-    <row r="307" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="307" spans="71:71">
       <c r="BS307" s="1" t="s">
         <v>1620</v>
       </c>
     </row>
-    <row r="308" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="308" spans="71:71">
       <c r="BS308" s="1" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="309" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="309" spans="71:71">
       <c r="BS309" s="1" t="s">
         <v>1622</v>
       </c>
     </row>
-    <row r="310" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="310" spans="71:71">
       <c r="BS310" s="1" t="s">
         <v>1623</v>
       </c>
     </row>
-    <row r="311" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="311" spans="71:71">
       <c r="BS311" s="1" t="s">
         <v>1624</v>
       </c>
     </row>
-    <row r="312" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="312" spans="71:71">
       <c r="BS312" s="1" t="s">
         <v>1625</v>
       </c>
     </row>
-    <row r="313" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="313" spans="71:71">
       <c r="BS313" s="1" t="s">
         <v>1626</v>
       </c>
     </row>
-    <row r="314" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="314" spans="71:71">
       <c r="BS314" s="1" t="s">
         <v>1627</v>
       </c>
     </row>
-    <row r="315" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="315" spans="71:71">
       <c r="BS315" s="1" t="s">
         <v>1628</v>
       </c>
     </row>
-    <row r="316" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="316" spans="71:71">
       <c r="BS316" s="1" t="s">
         <v>1629</v>
       </c>
     </row>
-    <row r="317" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="317" spans="71:71">
       <c r="BS317" s="1" t="s">
         <v>1630</v>
       </c>
     </row>
-    <row r="318" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="318" spans="71:71">
       <c r="BS318" s="1" t="s">
         <v>1631</v>
       </c>
     </row>
-    <row r="319" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="319" spans="71:71">
       <c r="BS319" s="1" t="s">
         <v>1632</v>
       </c>
     </row>
-    <row r="320" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="320" spans="71:71">
       <c r="BS320" s="1" t="s">
         <v>1633</v>
       </c>
     </row>
-    <row r="321" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="321" spans="71:71">
       <c r="BS321" s="1" t="s">
         <v>1634</v>
       </c>
     </row>
-    <row r="322" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="322" spans="71:71">
       <c r="BS322" s="1" t="s">
         <v>1635</v>
       </c>
     </row>
-    <row r="323" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="323" spans="71:71">
       <c r="BS323" s="1" t="s">
         <v>1636</v>
       </c>
     </row>
-    <row r="324" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="324" spans="71:71">
       <c r="BS324" s="1" t="s">
         <v>1637</v>
       </c>
     </row>
-    <row r="325" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="325" spans="71:71">
       <c r="BS325" s="1" t="s">
         <v>1638</v>
       </c>
     </row>
-    <row r="326" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="326" spans="71:71">
       <c r="BS326" s="1" t="s">
         <v>1639</v>
       </c>
     </row>
-    <row r="327" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="327" spans="71:71">
       <c r="BS327" s="1" t="s">
         <v>1640</v>
       </c>
     </row>
-    <row r="328" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="328" spans="71:71">
       <c r="BS328" s="1" t="s">
         <v>1641</v>
       </c>
     </row>
-    <row r="329" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="329" spans="71:71">
       <c r="BS329" s="1" t="s">
         <v>1642</v>
       </c>
     </row>
-    <row r="330" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="330" spans="71:71">
       <c r="BS330" s="1" t="s">
         <v>1643</v>
       </c>
     </row>
-    <row r="331" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="331" spans="71:71">
       <c r="BS331" s="1" t="s">
         <v>1644</v>
       </c>
     </row>
-    <row r="332" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="332" spans="71:71">
       <c r="BS332" s="1" t="s">
         <v>1645</v>
       </c>
     </row>
-    <row r="333" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="333" spans="71:71">
       <c r="BS333" s="1" t="s">
         <v>1646</v>
       </c>
     </row>
-    <row r="334" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="334" spans="71:71">
       <c r="BS334" s="1" t="s">
         <v>1647</v>
       </c>
     </row>
-    <row r="335" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="335" spans="71:71">
       <c r="BS335" s="1" t="s">
         <v>1648</v>
       </c>
     </row>
-    <row r="336" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="336" spans="71:71">
       <c r="BS336" s="1" t="s">
         <v>1649</v>
       </c>
     </row>
-    <row r="337" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="337" spans="71:71">
       <c r="BS337" s="1" t="s">
         <v>1650</v>
       </c>
     </row>
-    <row r="338" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="338" spans="71:71">
       <c r="BS338" s="1" t="s">
         <v>1651</v>
       </c>
     </row>
-    <row r="339" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="339" spans="71:71">
       <c r="BS339" s="1" t="s">
         <v>1652</v>
       </c>
     </row>
-    <row r="340" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="340" spans="71:71">
       <c r="BS340" s="1" t="s">
         <v>1653</v>
       </c>
     </row>
-    <row r="341" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="341" spans="71:71">
       <c r="BS341" s="1" t="s">
         <v>1654</v>
       </c>
     </row>
-    <row r="342" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="342" spans="71:71">
       <c r="BS342" s="1" t="s">
         <v>1655</v>
       </c>
     </row>
-    <row r="343" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="343" spans="71:71">
       <c r="BS343" s="1" t="s">
         <v>1656</v>
       </c>
     </row>
-    <row r="344" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="344" spans="71:71">
       <c r="BS344" s="1" t="s">
         <v>1657</v>
       </c>
     </row>
-    <row r="345" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="345" spans="71:71">
       <c r="BS345" s="1" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="346" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="346" spans="71:71">
       <c r="BS346" s="1" t="s">
         <v>1659</v>
       </c>
     </row>
-    <row r="347" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="347" spans="71:71">
       <c r="BS347" s="1" t="s">
         <v>1660</v>
       </c>
     </row>
-    <row r="348" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="348" spans="71:71">
       <c r="BS348" s="1" t="s">
         <v>1661</v>
       </c>
     </row>
-    <row r="349" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="349" spans="71:71">
       <c r="BS349" s="1" t="s">
         <v>1662</v>
       </c>
     </row>
-    <row r="350" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="350" spans="71:71">
       <c r="BS350" s="1" t="s">
         <v>1663</v>
       </c>
     </row>
-    <row r="351" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="351" spans="71:71">
       <c r="BS351" s="1" t="s">
         <v>1664</v>
       </c>
     </row>
-    <row r="352" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="352" spans="71:71">
       <c r="BS352" s="1" t="s">
         <v>1665</v>
       </c>
     </row>
-    <row r="353" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="353" spans="71:71">
       <c r="BS353" s="1" t="s">
         <v>1666</v>
       </c>
     </row>
-    <row r="354" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="354" spans="71:71">
       <c r="BS354" s="1" t="s">
         <v>1667</v>
       </c>
     </row>
-    <row r="355" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="355" spans="71:71">
       <c r="BS355" s="1" t="s">
         <v>1668</v>
       </c>
     </row>
-    <row r="356" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="356" spans="71:71">
       <c r="BS356" s="1" t="s">
         <v>1669</v>
       </c>
     </row>
-    <row r="357" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="357" spans="71:71">
       <c r="BS357" s="1" t="s">
         <v>1670</v>
       </c>
     </row>
-    <row r="358" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="358" spans="71:71">
       <c r="BS358" s="1" t="s">
         <v>1671</v>
       </c>
     </row>
-    <row r="359" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="359" spans="71:71">
       <c r="BS359" s="1" t="s">
         <v>1672</v>
       </c>
     </row>
-    <row r="360" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="360" spans="71:71">
       <c r="BS360" s="1" t="s">
         <v>1673</v>
       </c>
     </row>
-    <row r="361" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="361" spans="71:71">
       <c r="BS361" s="1" t="s">
         <v>1674</v>
       </c>
     </row>
-    <row r="362" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="362" spans="71:71">
       <c r="BS362" s="1" t="s">
         <v>1675</v>
       </c>
     </row>
-    <row r="363" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="363" spans="71:71">
       <c r="BS363" s="1" t="s">
         <v>1676</v>
       </c>
     </row>
-    <row r="364" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="364" spans="71:71">
       <c r="BS364" s="1" t="s">
         <v>1677</v>
       </c>
     </row>
-    <row r="365" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="365" spans="71:71">
       <c r="BS365" s="1" t="s">
         <v>1678</v>
       </c>
     </row>
-    <row r="366" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="366" spans="71:71">
       <c r="BS366" s="1" t="s">
         <v>1679</v>
       </c>
     </row>
-    <row r="367" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="367" spans="71:71">
       <c r="BS367" s="1" t="s">
         <v>1680</v>
       </c>
     </row>
-    <row r="368" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="368" spans="71:71">
       <c r="BS368" s="1" t="s">
         <v>1681</v>
       </c>
     </row>
-    <row r="369" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="369" spans="71:71">
       <c r="BS369" s="1" t="s">
         <v>1682</v>
       </c>
     </row>
-    <row r="370" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="370" spans="71:71">
       <c r="BS370" s="1" t="s">
         <v>1683</v>
       </c>
     </row>
-    <row r="371" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="371" spans="71:71">
       <c r="BS371" s="1" t="s">
         <v>1684</v>
       </c>
     </row>
-    <row r="372" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="372" spans="71:71">
       <c r="BS372" s="1" t="s">
         <v>1685</v>
       </c>
     </row>
-    <row r="373" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="373" spans="71:71">
       <c r="BS373" s="1" t="s">
         <v>1686</v>
       </c>
     </row>
-    <row r="374" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="374" spans="71:71">
       <c r="BS374" s="1" t="s">
         <v>1687</v>
       </c>
     </row>
-    <row r="375" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="375" spans="71:71">
       <c r="BS375" s="1" t="s">
         <v>1688</v>
       </c>
     </row>
-    <row r="376" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="376" spans="71:71">
       <c r="BS376" s="1" t="s">
         <v>1689</v>
       </c>
     </row>
-    <row r="377" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="377" spans="71:71">
       <c r="BS377" s="1" t="s">
         <v>1690</v>
       </c>
     </row>
-    <row r="378" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="378" spans="71:71">
       <c r="BS378" s="1" t="s">
         <v>1691</v>
       </c>
     </row>
-    <row r="379" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="379" spans="71:71">
       <c r="BS379" s="1" t="s">
         <v>1692</v>
       </c>
     </row>
-    <row r="380" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="380" spans="71:71">
       <c r="BS380" s="1" t="s">
         <v>1693</v>
       </c>
     </row>
-    <row r="381" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="381" spans="71:71">
       <c r="BS381" s="1" t="s">
         <v>1694</v>
       </c>
     </row>
-    <row r="382" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="382" spans="71:71">
       <c r="BS382" s="1" t="s">
         <v>1695</v>
       </c>
     </row>
-    <row r="383" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="383" spans="71:71">
       <c r="BS383" s="1" t="s">
         <v>1696</v>
       </c>
     </row>
-    <row r="384" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="384" spans="71:71">
       <c r="BS384" s="1" t="s">
         <v>1697</v>
       </c>
     </row>
-    <row r="385" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="385" spans="71:71">
       <c r="BS385" s="1" t="s">
         <v>1698</v>
       </c>
     </row>
-    <row r="386" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="386" spans="71:71">
       <c r="BS386" s="1" t="s">
         <v>1699</v>
       </c>
     </row>
-    <row r="387" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="387" spans="71:71">
       <c r="BS387" s="1" t="s">
         <v>1700</v>
       </c>
     </row>
-    <row r="388" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="388" spans="71:71">
       <c r="BS388" s="1" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="389" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="389" spans="71:71">
       <c r="BS389" s="1" t="s">
         <v>1702</v>
       </c>
     </row>
-    <row r="390" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="390" spans="71:71">
       <c r="BS390" s="1" t="s">
         <v>1703</v>
       </c>
     </row>
-    <row r="391" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="391" spans="71:71">
       <c r="BS391" s="1" t="s">
         <v>1704</v>
       </c>
     </row>
-    <row r="392" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="392" spans="71:71">
       <c r="BS392" s="1" t="s">
         <v>1705</v>
       </c>
     </row>
-    <row r="393" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="393" spans="71:71">
       <c r="BS393" s="1" t="s">
         <v>1706</v>
       </c>
     </row>
-    <row r="394" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="394" spans="71:71">
       <c r="BS394" s="1" t="s">
         <v>1707</v>
       </c>
     </row>
-    <row r="395" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="395" spans="71:71">
       <c r="BS395" s="1" t="s">
         <v>1708</v>
       </c>
     </row>
-    <row r="396" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="396" spans="71:71">
       <c r="BS396" s="1" t="s">
         <v>1709</v>
       </c>
     </row>
-    <row r="397" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="397" spans="71:71">
       <c r="BS397" s="1" t="s">
         <v>1710</v>
       </c>
     </row>
-    <row r="398" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="398" spans="71:71">
       <c r="BS398" s="1" t="s">
         <v>1711</v>
       </c>
     </row>
-    <row r="399" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="399" spans="71:71">
       <c r="BS399" s="1" t="s">
         <v>1712</v>
       </c>
     </row>
-    <row r="400" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="400" spans="71:71">
       <c r="BS400" s="1" t="s">
         <v>1713</v>
       </c>
     </row>
-    <row r="401" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="401" spans="71:71">
       <c r="BS401" s="1" t="s">
         <v>1714</v>
       </c>
     </row>
-    <row r="402" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="402" spans="71:71">
       <c r="BS402" s="1" t="s">
         <v>1715</v>
       </c>
     </row>
-    <row r="403" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="403" spans="71:71">
       <c r="BS403" s="1" t="s">
         <v>1716</v>
       </c>
     </row>
-    <row r="404" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="404" spans="71:71">
       <c r="BS404" s="1" t="s">
         <v>1717</v>
       </c>
     </row>
-    <row r="405" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="405" spans="71:71">
       <c r="BS405" s="1" t="s">
         <v>1718</v>
       </c>
     </row>
-    <row r="406" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="406" spans="71:71">
       <c r="BS406" s="1" t="s">
         <v>1719</v>
       </c>
     </row>
-    <row r="407" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="407" spans="71:71">
       <c r="BS407" s="1" t="s">
         <v>1720</v>
       </c>
     </row>
-    <row r="408" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="408" spans="71:71">
       <c r="BS408" s="1" t="s">
         <v>1721</v>
       </c>
     </row>
-    <row r="409" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="409" spans="71:71">
       <c r="BS409" s="1" t="s">
         <v>1722</v>
       </c>
     </row>
-    <row r="410" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="410" spans="71:71">
       <c r="BS410" s="1" t="s">
         <v>1723</v>
       </c>
     </row>
-    <row r="411" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="411" spans="71:71">
       <c r="BS411" s="1" t="s">
         <v>1724</v>
       </c>
     </row>
-    <row r="412" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="412" spans="71:71">
       <c r="BS412" s="1" t="s">
         <v>1725</v>
       </c>
     </row>
-    <row r="413" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="413" spans="71:71">
       <c r="BS413" s="1" t="s">
         <v>1726</v>
       </c>
     </row>
-    <row r="414" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="414" spans="71:71">
       <c r="BS414" s="1" t="s">
         <v>1727</v>
       </c>
     </row>
-    <row r="415" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="415" spans="71:71">
       <c r="BS415" s="1" t="s">
         <v>1728</v>
       </c>
     </row>
-    <row r="416" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="416" spans="71:71">
       <c r="BS416" s="1" t="s">
         <v>1729</v>
       </c>
     </row>
-    <row r="417" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="417" spans="71:71">
       <c r="BS417" s="1" t="s">
         <v>1730</v>
       </c>
     </row>
-    <row r="418" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="418" spans="71:71">
       <c r="BS418" s="1" t="s">
         <v>1731</v>
       </c>
     </row>
-    <row r="419" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="419" spans="71:71">
       <c r="BS419" s="1" t="s">
         <v>1732</v>
       </c>
     </row>
-    <row r="420" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="420" spans="71:71">
       <c r="BS420" s="1" t="s">
         <v>1733</v>
       </c>
     </row>
-    <row r="421" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="421" spans="71:71">
       <c r="BS421" s="1" t="s">
         <v>1734</v>
       </c>
     </row>
-    <row r="422" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="422" spans="71:71">
       <c r="BS422" s="1" t="s">
         <v>1735</v>
       </c>
     </row>
-    <row r="423" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="423" spans="71:71">
       <c r="BS423" s="1" t="s">
         <v>1736</v>
       </c>
     </row>
-    <row r="424" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="424" spans="71:71">
       <c r="BS424" s="1" t="s">
         <v>1737</v>
       </c>
     </row>
-    <row r="425" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="425" spans="71:71">
       <c r="BS425" s="1" t="s">
         <v>1738</v>
       </c>
     </row>
-    <row r="426" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="426" spans="71:71">
       <c r="BS426" s="1" t="s">
         <v>1739</v>
       </c>
     </row>
-    <row r="427" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="427" spans="71:71">
       <c r="BS427" s="1" t="s">
         <v>1740</v>
       </c>
     </row>
-    <row r="428" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="428" spans="71:71">
       <c r="BS428" s="1" t="s">
         <v>1741</v>
       </c>
     </row>
-    <row r="429" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="429" spans="71:71">
       <c r="BS429" s="1" t="s">
         <v>1742</v>
       </c>
     </row>
-    <row r="430" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="430" spans="71:71">
       <c r="BS430" s="1" t="s">
         <v>1743</v>
       </c>
     </row>
-    <row r="431" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="431" spans="71:71">
       <c r="BS431" s="1" t="s">
         <v>1744</v>
       </c>
     </row>
-    <row r="432" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="432" spans="71:71">
       <c r="BS432" s="1" t="s">
         <v>1745</v>
       </c>
     </row>
-    <row r="433" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="433" spans="71:71">
       <c r="BS433" s="1" t="s">
         <v>1746</v>
       </c>
     </row>
-    <row r="434" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="434" spans="71:71">
       <c r="BS434" s="1" t="s">
         <v>1747</v>
       </c>
     </row>
-    <row r="435" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="435" spans="71:71">
       <c r="BS435" s="1" t="s">
         <v>1748</v>
       </c>
     </row>
-    <row r="436" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="436" spans="71:71">
       <c r="BS436" s="1" t="s">
         <v>1749</v>
       </c>
     </row>
-    <row r="437" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="437" spans="71:71">
       <c r="BS437" s="1" t="s">
         <v>1750</v>
       </c>
     </row>
-    <row r="438" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="438" spans="71:71">
       <c r="BS438" s="1" t="s">
         <v>1751</v>
       </c>
     </row>
-    <row r="439" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="439" spans="71:71">
       <c r="BS439" s="1" t="s">
         <v>1752</v>
       </c>
     </row>
-    <row r="440" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="440" spans="71:71">
       <c r="BS440" s="1" t="s">
         <v>1753</v>
       </c>
     </row>
-    <row r="441" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="441" spans="71:71">
       <c r="BS441" s="1" t="s">
         <v>1754</v>
       </c>
     </row>
-    <row r="442" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="442" spans="71:71">
       <c r="BS442" s="1" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="443" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="443" spans="71:71">
       <c r="BS443" s="1" t="s">
         <v>1756</v>
       </c>
     </row>
-    <row r="444" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="444" spans="71:71">
       <c r="BS444" s="1" t="s">
         <v>1757</v>
       </c>
     </row>
-    <row r="445" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="445" spans="71:71">
       <c r="BS445" s="1" t="s">
         <v>1758</v>
       </c>
     </row>
-    <row r="446" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="446" spans="71:71">
       <c r="BS446" s="1" t="s">
         <v>1759</v>
       </c>
     </row>
-    <row r="447" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="447" spans="71:71">
       <c r="BS447" s="1" t="s">
         <v>1760</v>
       </c>
     </row>
-    <row r="448" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="448" spans="71:71">
       <c r="BS448" s="1" t="s">
         <v>1761</v>
       </c>
     </row>
-    <row r="449" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="449" spans="71:71">
       <c r="BS449" s="1" t="s">
         <v>1762</v>
       </c>
     </row>
-    <row r="450" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="450" spans="71:71">
       <c r="BS450" s="1" t="s">
         <v>1763</v>
       </c>
     </row>
-    <row r="451" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="451" spans="71:71">
       <c r="BS451" s="1" t="s">
         <v>1764</v>
       </c>
     </row>
-    <row r="452" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="452" spans="71:71">
       <c r="BS452" s="1" t="s">
         <v>1765</v>
       </c>
     </row>
-    <row r="453" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="453" spans="71:71">
       <c r="BS453" s="1" t="s">
         <v>1766</v>
       </c>
     </row>
-    <row r="454" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="454" spans="71:71">
       <c r="BS454" s="1" t="s">
         <v>1767</v>
       </c>
     </row>
-    <row r="455" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="455" spans="71:71">
       <c r="BS455" s="1" t="s">
         <v>1768</v>
       </c>
     </row>
-    <row r="456" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="456" spans="71:71">
       <c r="BS456" s="1" t="s">
         <v>1769</v>
       </c>
     </row>
-    <row r="457" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="457" spans="71:71">
       <c r="BS457" s="1" t="s">
         <v>1770</v>
       </c>
     </row>
-    <row r="458" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="458" spans="71:71">
       <c r="BS458" s="1" t="s">
         <v>1771</v>
       </c>
     </row>
-    <row r="459" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="459" spans="71:71">
       <c r="BS459" s="1" t="s">
         <v>1772</v>
       </c>
     </row>
-    <row r="460" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="460" spans="71:71">
       <c r="BS460" s="1" t="s">
         <v>1773</v>
       </c>
     </row>
-    <row r="461" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="461" spans="71:71">
       <c r="BS461" s="1" t="s">
         <v>1774</v>
       </c>
     </row>
-    <row r="462" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="462" spans="71:71">
       <c r="BS462" s="1" t="s">
         <v>1775</v>
       </c>
     </row>
-    <row r="463" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="463" spans="71:71">
       <c r="BS463" s="1" t="s">
         <v>1776</v>
       </c>
     </row>
-    <row r="464" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="464" spans="71:71">
       <c r="BS464" s="1" t="s">
         <v>1777</v>
       </c>
     </row>
-    <row r="465" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="465" spans="71:71">
       <c r="BS465" s="1" t="s">
         <v>1778</v>
       </c>
     </row>
-    <row r="466" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="466" spans="71:71">
       <c r="BS466" s="1" t="s">
         <v>1779</v>
       </c>
     </row>
-    <row r="467" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="467" spans="71:71">
       <c r="BS467" s="1" t="s">
         <v>1780</v>
       </c>
     </row>
-    <row r="468" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="468" spans="71:71">
       <c r="BS468" s="1" t="s">
         <v>1781</v>
       </c>
     </row>
-    <row r="469" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="469" spans="71:71">
       <c r="BS469" s="1" t="s">
         <v>1782</v>
       </c>
     </row>
-    <row r="470" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="470" spans="71:71">
       <c r="BS470" s="1" t="s">
         <v>1783</v>
       </c>
     </row>
-    <row r="471" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="471" spans="71:71">
       <c r="BS471" s="1" t="s">
         <v>1784</v>
       </c>
     </row>
-    <row r="472" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="472" spans="71:71">
       <c r="BS472" s="1" t="s">
         <v>1785</v>
       </c>
     </row>
-    <row r="473" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="473" spans="71:71">
       <c r="BS473" s="1" t="s">
         <v>1786</v>
       </c>
     </row>
-    <row r="474" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="474" spans="71:71">
       <c r="BS474" s="1" t="s">
         <v>1787</v>
       </c>
     </row>
-    <row r="475" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="475" spans="71:71">
       <c r="BS475" s="1" t="s">
         <v>1788</v>
       </c>
     </row>
-    <row r="476" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="476" spans="71:71">
       <c r="BS476" s="1" t="s">
         <v>1789</v>
       </c>
     </row>
-    <row r="477" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="477" spans="71:71">
       <c r="BS477" s="1" t="s">
         <v>1790</v>
       </c>
     </row>
-    <row r="478" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="478" spans="71:71">
       <c r="BS478" s="1" t="s">
         <v>1791</v>
       </c>
     </row>
-    <row r="479" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="479" spans="71:71">
       <c r="BS479" s="1" t="s">
         <v>1792</v>
       </c>
     </row>
-    <row r="480" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="480" spans="71:71">
       <c r="BS480" s="1" t="s">
         <v>1793</v>
       </c>
     </row>
-    <row r="481" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="481" spans="71:71">
       <c r="BS481" s="1" t="s">
         <v>1794</v>
       </c>
     </row>
-    <row r="482" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="482" spans="71:71">
       <c r="BS482" s="1" t="s">
         <v>1795</v>
       </c>
     </row>
-    <row r="483" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="483" spans="71:71">
       <c r="BS483" s="1" t="s">
         <v>1796</v>
       </c>
     </row>
-    <row r="484" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="484" spans="71:71">
       <c r="BS484" s="1" t="s">
         <v>1797</v>
       </c>
     </row>
-    <row r="485" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="485" spans="71:71">
       <c r="BS485" s="1" t="s">
         <v>1798</v>
       </c>
     </row>
-    <row r="486" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="486" spans="71:71">
       <c r="BS486" s="1" t="s">
         <v>1799</v>
       </c>
     </row>
-    <row r="487" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="487" spans="71:71">
       <c r="BS487" s="1" t="s">
         <v>1800</v>
       </c>
     </row>
-    <row r="488" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="488" spans="71:71">
       <c r="BS488" s="1" t="s">
         <v>1801</v>
       </c>
     </row>
-    <row r="489" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="489" spans="71:71">
       <c r="BS489" s="1" t="s">
         <v>1802</v>
       </c>
     </row>
-    <row r="490" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="490" spans="71:71">
       <c r="BS490" s="1" t="s">
         <v>1803</v>
       </c>
     </row>
-    <row r="491" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="491" spans="71:71">
       <c r="BS491" s="1" t="s">
         <v>1804</v>
       </c>
     </row>
-    <row r="492" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="492" spans="71:71">
       <c r="BS492" s="1" t="s">
         <v>1805</v>
       </c>
     </row>
-    <row r="493" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="493" spans="71:71">
       <c r="BS493" s="1" t="s">
         <v>1806</v>
       </c>
     </row>
-    <row r="494" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="494" spans="71:71">
       <c r="BS494" s="1" t="s">
         <v>1807</v>
       </c>
     </row>
-    <row r="495" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="495" spans="71:71">
       <c r="BS495" s="1" t="s">
         <v>1808</v>
       </c>
     </row>
-    <row r="496" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="496" spans="71:71">
       <c r="BS496" s="1" t="s">
         <v>1809</v>
       </c>
     </row>
-    <row r="497" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="497" spans="71:71">
       <c r="BS497" s="1" t="s">
         <v>1810</v>
       </c>
     </row>
-    <row r="498" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="498" spans="71:71">
       <c r="BS498" s="1" t="s">
         <v>1811</v>
       </c>
     </row>
-    <row r="499" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="499" spans="71:71">
       <c r="BS499" s="1" t="s">
         <v>1812</v>
       </c>
     </row>
-    <row r="500" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="500" spans="71:71">
       <c r="BS500" s="1" t="s">
         <v>1813</v>
       </c>
     </row>
-    <row r="501" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="501" spans="71:71">
       <c r="BS501" s="1" t="s">
         <v>1814</v>
       </c>
     </row>
-    <row r="502" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="502" spans="71:71">
       <c r="BS502" s="1" t="s">
         <v>1815</v>
       </c>
     </row>
-    <row r="503" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="503" spans="71:71">
       <c r="BS503" s="1" t="s">
         <v>1816</v>
       </c>
     </row>
-    <row r="504" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="504" spans="71:71">
       <c r="BS504" s="1" t="s">
         <v>1817</v>
       </c>
     </row>
-    <row r="505" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="505" spans="71:71">
       <c r="BS505" s="1" t="s">
         <v>1818</v>
       </c>
     </row>
-    <row r="506" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="506" spans="71:71">
       <c r="BS506" s="1" t="s">
         <v>1819</v>
       </c>
     </row>
-    <row r="507" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="507" spans="71:71">
       <c r="BS507" s="1" t="s">
         <v>1820</v>
       </c>
     </row>
-    <row r="508" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="508" spans="71:71">
       <c r="BS508" s="1" t="s">
         <v>1821</v>
       </c>
     </row>
-    <row r="509" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="509" spans="71:71">
       <c r="BS509" s="1" t="s">
         <v>1822</v>
       </c>
     </row>
-    <row r="510" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="510" spans="71:71">
       <c r="BS510" s="1" t="s">
         <v>1823</v>
       </c>
     </row>
-    <row r="511" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="511" spans="71:71">
       <c r="BS511" s="1" t="s">
         <v>1824</v>
       </c>
     </row>
-    <row r="512" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="512" spans="71:71">
       <c r="BS512" s="1" t="s">
         <v>1825</v>
       </c>
     </row>
-    <row r="513" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="513" spans="71:71">
       <c r="BS513" s="1" t="s">
         <v>1826</v>
       </c>
     </row>
-    <row r="514" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="514" spans="71:71">
       <c r="BS514" s="1" t="s">
         <v>1827</v>
       </c>
     </row>
-    <row r="515" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="515" spans="71:71">
       <c r="BS515" s="1" t="s">
         <v>1828</v>
       </c>
     </row>
-    <row r="516" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="516" spans="71:71">
       <c r="BS516" s="1" t="s">
         <v>1829</v>
       </c>
     </row>
-    <row r="517" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="517" spans="71:71">
       <c r="BS517" s="1" t="s">
         <v>1830</v>
       </c>
     </row>
-    <row r="518" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="518" spans="71:71">
       <c r="BS518" s="1" t="s">
         <v>1831</v>
       </c>
     </row>
-    <row r="519" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="519" spans="71:71">
       <c r="BS519" s="1" t="s">
         <v>1832</v>
       </c>
     </row>
-    <row r="520" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="520" spans="71:71">
       <c r="BS520" s="1" t="s">
         <v>1833</v>
       </c>
     </row>
-    <row r="521" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="521" spans="71:71">
       <c r="BS521" s="1" t="s">
         <v>1834</v>
       </c>
     </row>
-    <row r="522" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="522" spans="71:71">
       <c r="BS522" s="1" t="s">
         <v>1835</v>
       </c>
     </row>
-    <row r="523" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="523" spans="71:71">
       <c r="BS523" s="1" t="s">
         <v>1836</v>
       </c>
     </row>
-    <row r="524" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="524" spans="71:71">
       <c r="BS524" s="1" t="s">
         <v>1837</v>
       </c>
     </row>
-    <row r="525" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="525" spans="71:71">
       <c r="BS525" s="1" t="s">
         <v>1838</v>
       </c>
     </row>
-    <row r="526" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="526" spans="71:71">
       <c r="BS526" s="1" t="s">
         <v>1839</v>
       </c>
     </row>
-    <row r="527" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="527" spans="71:71">
       <c r="BS527" s="1" t="s">
         <v>1840</v>
       </c>
     </row>
-    <row r="528" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="528" spans="71:71">
       <c r="BS528" s="1" t="s">
         <v>1841</v>
       </c>
     </row>
-    <row r="529" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="529" spans="71:71">
       <c r="BS529" s="1" t="s">
         <v>1842</v>
       </c>
     </row>
-    <row r="530" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="530" spans="71:71">
       <c r="BS530" s="1" t="s">
         <v>1843</v>
       </c>
     </row>
-    <row r="531" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="531" spans="71:71">
       <c r="BS531" s="1" t="s">
         <v>1844</v>
       </c>
     </row>
-    <row r="532" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="532" spans="71:71">
       <c r="BS532" s="1" t="s">
         <v>1845</v>
       </c>
     </row>
-    <row r="533" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="533" spans="71:71">
       <c r="BS533" s="1" t="s">
         <v>1846</v>
       </c>
     </row>
-    <row r="534" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="534" spans="71:71">
       <c r="BS534" s="1" t="s">
         <v>1847</v>
       </c>
     </row>
-    <row r="535" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="535" spans="71:71">
       <c r="BS535" s="1" t="s">
         <v>1848</v>
       </c>
     </row>
-    <row r="536" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="536" spans="71:71">
       <c r="BS536" s="1" t="s">
         <v>1849</v>
       </c>
     </row>
-    <row r="537" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="537" spans="71:71">
       <c r="BS537" s="1" t="s">
         <v>1850</v>
       </c>
     </row>
-    <row r="538" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="538" spans="71:71">
       <c r="BS538" s="1" t="s">
         <v>1851</v>
       </c>
     </row>
-    <row r="539" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="539" spans="71:71">
       <c r="BS539" s="1" t="s">
         <v>1852</v>
       </c>
     </row>
-    <row r="540" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="540" spans="71:71">
       <c r="BS540" s="1" t="s">
         <v>1853</v>
       </c>
     </row>
-    <row r="541" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="541" spans="71:71">
       <c r="BS541" s="1" t="s">
         <v>1854</v>
       </c>
     </row>
-    <row r="542" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="542" spans="71:71">
       <c r="BS542" s="1" t="s">
         <v>1855</v>
       </c>
     </row>
-    <row r="543" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="543" spans="71:71">
       <c r="BS543" s="1" t="s">
         <v>1856</v>
       </c>
     </row>
-    <row r="544" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="544" spans="71:71">
       <c r="BS544" s="1" t="s">
         <v>1857</v>
       </c>
     </row>
-    <row r="545" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="545" spans="71:71">
       <c r="BS545" s="1" t="s">
         <v>1858</v>
       </c>
     </row>
-    <row r="546" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="546" spans="71:71">
       <c r="BS546" s="1" t="s">
         <v>1859</v>
       </c>
     </row>
-    <row r="547" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="547" spans="71:71">
       <c r="BS547" s="1" t="s">
         <v>1860</v>
       </c>
     </row>
-    <row r="548" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="548" spans="71:71">
       <c r="BS548" s="1" t="s">
         <v>1861</v>
       </c>
     </row>
-    <row r="549" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="549" spans="71:71">
       <c r="BS549" s="1" t="s">
         <v>1862</v>
       </c>
     </row>
-    <row r="550" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="550" spans="71:71">
       <c r="BS550" s="1" t="s">
         <v>1863</v>
       </c>
     </row>
-    <row r="551" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="551" spans="71:71">
       <c r="BS551" s="1" t="s">
         <v>1864</v>
       </c>
     </row>
-    <row r="552" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="552" spans="71:71">
       <c r="BS552" s="1" t="s">
         <v>1865</v>
       </c>
     </row>
-    <row r="553" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="553" spans="71:71">
       <c r="BS553" s="1" t="s">
         <v>1866</v>
       </c>
     </row>
-    <row r="554" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="554" spans="71:71">
       <c r="BS554" s="1" t="s">
         <v>1867</v>
       </c>
     </row>
-    <row r="555" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="555" spans="71:71">
       <c r="BS555" s="1" t="s">
         <v>1868</v>
       </c>
     </row>
-    <row r="556" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="556" spans="71:71">
       <c r="BS556" s="1" t="s">
         <v>1869</v>
       </c>
     </row>
-    <row r="557" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="557" spans="71:71">
       <c r="BS557" s="1" t="s">
         <v>1870</v>
       </c>
     </row>
-    <row r="558" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="558" spans="71:71">
       <c r="BS558" s="1" t="s">
         <v>1871</v>
       </c>
     </row>
-    <row r="559" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="559" spans="71:71">
       <c r="BS559" s="1" t="s">
         <v>1872</v>
       </c>
     </row>
-    <row r="560" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="560" spans="71:71">
       <c r="BS560" s="1" t="s">
         <v>1873</v>
       </c>
     </row>
-    <row r="561" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="561" spans="71:71">
       <c r="BS561" s="1" t="s">
         <v>1874</v>
       </c>
     </row>
-    <row r="562" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="562" spans="71:71">
       <c r="BS562" s="1" t="s">
         <v>1875</v>
       </c>
     </row>
-    <row r="563" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="563" spans="71:71">
       <c r="BS563" s="1" t="s">
         <v>1876</v>
       </c>
     </row>
-    <row r="564" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="564" spans="71:71">
       <c r="BS564" s="1" t="s">
         <v>1877</v>
       </c>
     </row>
-    <row r="565" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="565" spans="71:71">
       <c r="BS565" s="1" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="566" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="566" spans="71:71">
       <c r="BS566" s="1" t="s">
         <v>1879</v>
       </c>
     </row>
-    <row r="567" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="567" spans="71:71">
       <c r="BS567" s="1" t="s">
         <v>1880</v>
       </c>
     </row>
-    <row r="568" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="568" spans="71:71">
       <c r="BS568" s="1" t="s">
         <v>1881</v>
       </c>
     </row>
-    <row r="569" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="569" spans="71:71">
       <c r="BS569" s="1" t="s">
         <v>1882</v>
       </c>
     </row>
-    <row r="570" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="570" spans="71:71">
       <c r="BS570" s="1" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="571" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="571" spans="71:71">
       <c r="BS571" s="1" t="s">
         <v>1884</v>
       </c>
     </row>
-    <row r="572" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="572" spans="71:71">
       <c r="BS572" s="1" t="s">
         <v>1885</v>
       </c>
     </row>
-    <row r="573" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="573" spans="71:71">
       <c r="BS573" s="1" t="s">
         <v>1886</v>
       </c>
     </row>
-    <row r="574" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="574" spans="71:71">
       <c r="BS574" s="1" t="s">
         <v>1887</v>
       </c>
     </row>
-    <row r="575" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="575" spans="71:71">
       <c r="BS575" s="1" t="s">
         <v>1888</v>
       </c>
     </row>
-    <row r="576" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="576" spans="71:71">
       <c r="BS576" s="1" t="s">
         <v>1889</v>
       </c>
     </row>
-    <row r="577" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="577" spans="71:71">
       <c r="BS577" s="1" t="s">
         <v>1890</v>
       </c>
     </row>
-    <row r="578" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="578" spans="71:71">
       <c r="BS578" s="1" t="s">
         <v>1891</v>
       </c>
     </row>
-    <row r="579" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="579" spans="71:71">
       <c r="BS579" s="1" t="s">
         <v>1892</v>
       </c>
     </row>
-    <row r="580" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="580" spans="71:71">
       <c r="BS580" s="1" t="s">
         <v>1893</v>
       </c>
     </row>
-    <row r="581" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="581" spans="71:71">
       <c r="BS581" s="1" t="s">
         <v>1894</v>
       </c>
     </row>
-    <row r="582" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="582" spans="71:71">
       <c r="BS582" s="1" t="s">
         <v>1895</v>
       </c>
     </row>
-    <row r="583" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="583" spans="71:71">
       <c r="BS583" s="1" t="s">
         <v>1896</v>
       </c>
     </row>
-    <row r="584" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="584" spans="71:71">
       <c r="BS584" s="1" t="s">
         <v>1897</v>
       </c>
     </row>
-    <row r="585" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="585" spans="71:71">
       <c r="BS585" s="1" t="s">
         <v>1898</v>
       </c>
     </row>
-    <row r="586" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="586" spans="71:71">
       <c r="BS586" s="1" t="s">
         <v>1899</v>
       </c>
     </row>
-    <row r="587" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="587" spans="71:71">
       <c r="BS587" s="1" t="s">
         <v>1900</v>
       </c>
     </row>
-    <row r="588" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="588" spans="71:71">
       <c r="BS588" s="1" t="s">
         <v>1901</v>
       </c>
     </row>
-    <row r="589" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="589" spans="71:71">
       <c r="BS589" s="1" t="s">
         <v>1902</v>
       </c>
     </row>
-    <row r="590" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="590" spans="71:71">
       <c r="BS590" s="1" t="s">
         <v>1903</v>
       </c>
     </row>
-    <row r="591" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="591" spans="71:71">
       <c r="BS591" s="1" t="s">
         <v>1904</v>
       </c>
     </row>
-    <row r="592" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="592" spans="71:71">
       <c r="BS592" s="1" t="s">
         <v>1905</v>
       </c>
     </row>
-    <row r="593" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="593" spans="71:71">
       <c r="BS593" s="1" t="s">
         <v>1906</v>
       </c>
     </row>
-    <row r="594" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="594" spans="71:71">
       <c r="BS594" s="1" t="s">
         <v>1907</v>
       </c>
     </row>
-    <row r="595" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="595" spans="71:71">
       <c r="BS595" s="1" t="s">
         <v>1908</v>
       </c>
     </row>
-    <row r="596" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="596" spans="71:71">
       <c r="BS596" s="1" t="s">
         <v>1909</v>
       </c>
     </row>
-    <row r="597" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="597" spans="71:71">
       <c r="BS597" s="1" t="s">
         <v>1910</v>
       </c>
     </row>
-    <row r="598" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="598" spans="71:71">
       <c r="BS598" s="1" t="s">
         <v>1911</v>
       </c>
     </row>
-    <row r="599" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="599" spans="71:71">
       <c r="BS599" s="1" t="s">
         <v>1912</v>
       </c>
     </row>
-    <row r="600" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="600" spans="71:71">
       <c r="BS600" s="1" t="s">
         <v>1913</v>
       </c>
     </row>
-    <row r="601" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="601" spans="71:71">
       <c r="BS601" s="1" t="s">
         <v>1914</v>
       </c>
     </row>
-    <row r="602" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="602" spans="71:71">
       <c r="BS602" s="1" t="s">
         <v>1915</v>
       </c>
     </row>
-    <row r="603" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="603" spans="71:71">
       <c r="BS603" s="1" t="s">
         <v>1916</v>
       </c>
     </row>
-    <row r="604" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="604" spans="71:71">
       <c r="BS604" s="1" t="s">
         <v>1917</v>
       </c>
     </row>
-    <row r="605" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="605" spans="71:71">
       <c r="BS605" s="1" t="s">
         <v>1918</v>
       </c>
     </row>
-    <row r="606" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="606" spans="71:71">
       <c r="BS606" s="1" t="s">
         <v>1919</v>
       </c>
     </row>
-    <row r="607" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="607" spans="71:71">
       <c r="BS607" s="1" t="s">
         <v>1920</v>
       </c>
     </row>
-    <row r="608" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="608" spans="71:71">
       <c r="BS608" s="1" t="s">
         <v>1921</v>
       </c>
     </row>
-    <row r="609" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="609" spans="71:71">
       <c r="BS609" s="1" t="s">
         <v>1922</v>
       </c>
     </row>
-    <row r="610" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="610" spans="71:71">
       <c r="BS610" s="1" t="s">
         <v>1923</v>
       </c>
     </row>
-    <row r="611" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="611" spans="71:71">
       <c r="BS611" s="1" t="s">
         <v>1924</v>
       </c>
     </row>
-    <row r="612" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="612" spans="71:71">
       <c r="BS612" s="1" t="s">
         <v>1925</v>
       </c>
     </row>
-    <row r="613" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="613" spans="71:71">
       <c r="BS613" s="1" t="s">
         <v>1926</v>
       </c>
     </row>
-    <row r="614" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="614" spans="71:71">
       <c r="BS614" s="1" t="s">
         <v>1927</v>
       </c>
     </row>
-    <row r="615" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="615" spans="71:71">
       <c r="BS615" s="1" t="s">
         <v>1928</v>
       </c>
     </row>
-    <row r="616" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="616" spans="71:71">
       <c r="BS616" s="1" t="s">
         <v>1929</v>
       </c>
     </row>
-    <row r="617" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="617" spans="71:71">
       <c r="BS617" s="1" t="s">
         <v>1930</v>
       </c>
     </row>
-    <row r="618" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="618" spans="71:71">
       <c r="BS618" s="1" t="s">
         <v>1931</v>
       </c>
     </row>
-    <row r="619" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="619" spans="71:71">
       <c r="BS619" s="1" t="s">
         <v>1932</v>
       </c>
     </row>
-    <row r="620" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="620" spans="71:71">
       <c r="BS620" s="1" t="s">
         <v>1933</v>
       </c>
     </row>
-    <row r="621" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="621" spans="71:71">
       <c r="BS621" s="1" t="s">
         <v>1934</v>
       </c>
     </row>
-    <row r="622" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="622" spans="71:71">
       <c r="BS622" s="1" t="s">
         <v>1935</v>
       </c>
     </row>
-    <row r="623" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="623" spans="71:71">
       <c r="BS623" s="1" t="s">
         <v>1936</v>
       </c>
     </row>
-    <row r="624" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="624" spans="71:71">
       <c r="BS624" s="1" t="s">
         <v>1937</v>
       </c>
     </row>
-    <row r="625" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="625" spans="71:71">
       <c r="BS625" s="1" t="s">
         <v>1938</v>
       </c>
     </row>
-    <row r="626" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="626" spans="71:71">
       <c r="BS626" s="1" t="s">
         <v>1939</v>
       </c>
     </row>
-    <row r="627" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="627" spans="71:71">
       <c r="BS627" s="1" t="s">
         <v>1940</v>
       </c>
     </row>
-    <row r="628" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="628" spans="71:71">
       <c r="BS628" s="1" t="s">
         <v>1941</v>
       </c>
     </row>
-    <row r="629" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="629" spans="71:71">
       <c r="BS629" s="1" t="s">
         <v>1942</v>
       </c>
     </row>
-    <row r="630" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="630" spans="71:71">
       <c r="BS630" s="1" t="s">
         <v>1943</v>
       </c>
     </row>
-    <row r="631" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="631" spans="71:71">
       <c r="BS631" s="1" t="s">
         <v>1944</v>
       </c>
     </row>
-    <row r="632" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="632" spans="71:71">
       <c r="BS632" s="1" t="s">
         <v>1945</v>
       </c>
     </row>
-    <row r="633" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="633" spans="71:71">
       <c r="BS633" s="1" t="s">
         <v>1946</v>
       </c>
     </row>
-    <row r="634" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="634" spans="71:71">
       <c r="BS634" s="1" t="s">
         <v>1947</v>
       </c>
     </row>
-    <row r="635" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="635" spans="71:71">
       <c r="BS635" s="1" t="s">
         <v>1948</v>
       </c>
     </row>
-    <row r="636" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="636" spans="71:71">
       <c r="BS636" s="1" t="s">
         <v>1949</v>
       </c>
     </row>
-    <row r="637" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="637" spans="71:71">
       <c r="BS637" s="1" t="s">
         <v>1950</v>
       </c>
     </row>
-    <row r="638" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="638" spans="71:71">
       <c r="BS638" s="1" t="s">
         <v>1951</v>
       </c>
     </row>
-    <row r="639" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="639" spans="71:71">
       <c r="BS639" s="1" t="s">
         <v>1952</v>
       </c>
     </row>
-    <row r="640" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="640" spans="71:71">
       <c r="BS640" s="1" t="s">
         <v>1953</v>
       </c>
     </row>
-    <row r="641" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="641" spans="71:71">
       <c r="BS641" s="1" t="s">
         <v>1954</v>
       </c>
     </row>
-    <row r="642" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="642" spans="71:71">
       <c r="BS642" s="1" t="s">
         <v>1955</v>
       </c>
     </row>
-    <row r="643" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="643" spans="71:71">
       <c r="BS643" s="1" t="s">
         <v>1956</v>
       </c>
     </row>
-    <row r="644" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="644" spans="71:71">
       <c r="BS644" s="1" t="s">
         <v>1957</v>
       </c>
     </row>
-    <row r="645" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="645" spans="71:71">
       <c r="BS645" s="1" t="s">
         <v>1958</v>
       </c>
     </row>
-    <row r="646" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="646" spans="71:71">
       <c r="BS646" s="1" t="s">
         <v>1959</v>
       </c>
     </row>
-    <row r="647" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="647" spans="71:71">
       <c r="BS647" s="1" t="s">
         <v>1960</v>
       </c>
     </row>
-    <row r="648" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="648" spans="71:71">
       <c r="BS648" s="1" t="s">
         <v>1961</v>
       </c>
     </row>
-    <row r="649" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="649" spans="71:71">
       <c r="BS649" s="1" t="s">
         <v>1962</v>
       </c>
     </row>
-    <row r="650" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="650" spans="71:71">
       <c r="BS650" s="1" t="s">
         <v>1963</v>
       </c>
     </row>
-    <row r="651" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="651" spans="71:71">
       <c r="BS651" s="1" t="s">
         <v>1964</v>
       </c>
     </row>
-    <row r="652" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="652" spans="71:71">
       <c r="BS652" s="1" t="s">
         <v>1965</v>
       </c>
     </row>
-    <row r="653" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="653" spans="71:71">
       <c r="BS653" s="1" t="s">
         <v>1966</v>
       </c>
     </row>
-    <row r="654" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="654" spans="71:71">
       <c r="BS654" s="1" t="s">
         <v>1967</v>
       </c>
     </row>
-    <row r="655" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="655" spans="71:71">
       <c r="BS655" s="1" t="s">
         <v>1968</v>
       </c>
     </row>
-    <row r="656" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="656" spans="71:71">
       <c r="BS656" s="1" t="s">
         <v>1969</v>
       </c>
     </row>
-    <row r="657" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="657" spans="71:71">
       <c r="BS657" s="1" t="s">
         <v>1970</v>
       </c>
     </row>
-    <row r="658" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="658" spans="71:71">
       <c r="BS658" s="1" t="s">
         <v>1971</v>
       </c>
     </row>
-    <row r="659" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="659" spans="71:71">
       <c r="BS659" s="1" t="s">
         <v>1972</v>
       </c>
     </row>
-    <row r="660" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="660" spans="71:71">
       <c r="BS660" s="1" t="s">
         <v>1973</v>
       </c>
     </row>
-    <row r="661" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="661" spans="71:71">
       <c r="BS661" s="1" t="s">
         <v>1974</v>
       </c>
     </row>
-    <row r="662" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="662" spans="71:71">
       <c r="BS662" s="1" t="s">
         <v>1975</v>
       </c>
     </row>
-    <row r="663" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="663" spans="71:71">
       <c r="BS663" s="1" t="s">
         <v>1976</v>
       </c>
     </row>
-    <row r="664" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="664" spans="71:71">
       <c r="BS664" s="1" t="s">
         <v>1977</v>
       </c>
     </row>
-    <row r="665" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="665" spans="71:71">
       <c r="BS665" s="1" t="s">
         <v>1978</v>
       </c>
     </row>
-    <row r="666" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="666" spans="71:71">
       <c r="BS666" s="1" t="s">
         <v>1979</v>
       </c>
     </row>
-    <row r="667" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="667" spans="71:71">
       <c r="BS667" s="1" t="s">
         <v>1980</v>
       </c>
     </row>
-    <row r="668" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="668" spans="71:71">
       <c r="BS668" s="1" t="s">
         <v>1981</v>
       </c>
     </row>
-    <row r="669" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="669" spans="71:71">
       <c r="BS669" s="1" t="s">
         <v>1982</v>
       </c>
     </row>
-    <row r="670" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="670" spans="71:71">
       <c r="BS670" s="1" t="s">
         <v>1983</v>
       </c>
     </row>
-    <row r="671" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="671" spans="71:71">
       <c r="BS671" s="1" t="s">
         <v>1984</v>
       </c>
     </row>
-    <row r="672" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="672" spans="71:71">
       <c r="BS672" s="1" t="s">
         <v>1985</v>
       </c>
     </row>
-    <row r="673" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="673" spans="71:71">
       <c r="BS673" s="1" t="s">
         <v>1986</v>
       </c>
     </row>
-    <row r="674" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="674" spans="71:71">
       <c r="BS674" s="1" t="s">
         <v>1987</v>
       </c>
     </row>
-    <row r="675" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="675" spans="71:71">
       <c r="BS675" s="1" t="s">
         <v>1988</v>
       </c>
     </row>
-    <row r="676" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="676" spans="71:71">
       <c r="BS676" s="1" t="s">
         <v>1989</v>
       </c>
     </row>
-    <row r="677" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="677" spans="71:71">
       <c r="BS677" s="1" t="s">
         <v>1990</v>
       </c>
     </row>
-    <row r="678" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="678" spans="71:71">
       <c r="BS678" s="1" t="s">
         <v>1991</v>
       </c>
     </row>
-    <row r="679" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="679" spans="71:71">
       <c r="BS679" s="1" t="s">
         <v>1992</v>
       </c>
     </row>
-    <row r="680" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="680" spans="71:71">
       <c r="BS680" s="1" t="s">
         <v>1993</v>
       </c>
     </row>
-    <row r="681" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="681" spans="71:71">
       <c r="BS681" s="1" t="s">
         <v>1994</v>
       </c>
     </row>
-    <row r="682" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="682" spans="71:71">
       <c r="BS682" s="1" t="s">
         <v>1995</v>
       </c>
     </row>
-    <row r="683" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="683" spans="71:71">
       <c r="BS683" s="1" t="s">
         <v>1996</v>
       </c>
     </row>
-    <row r="684" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="684" spans="71:71">
       <c r="BS684" s="1" t="s">
         <v>1997</v>
       </c>
     </row>
-    <row r="685" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="685" spans="71:71">
       <c r="BS685" s="1" t="s">
         <v>1998</v>
       </c>
     </row>
-    <row r="686" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="686" spans="71:71">
       <c r="BS686" s="1" t="s">
         <v>1999</v>
       </c>
     </row>
-    <row r="687" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="687" spans="71:71">
       <c r="BS687" s="1" t="s">
         <v>2000</v>
       </c>
     </row>
-    <row r="688" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="688" spans="71:71">
       <c r="BS688" s="1" t="s">
         <v>2001</v>
       </c>
     </row>
-    <row r="689" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="689" spans="71:71">
       <c r="BS689" s="1" t="s">
         <v>2002</v>
       </c>
     </row>
-    <row r="690" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="690" spans="71:71">
       <c r="BS690" s="1" t="s">
         <v>2003</v>
       </c>
     </row>
-    <row r="691" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="691" spans="71:71">
       <c r="BS691" s="1" t="s">
         <v>2004</v>
       </c>
     </row>
-    <row r="692" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="692" spans="71:71">
       <c r="BS692" s="1" t="s">
         <v>2005</v>
       </c>
     </row>
-    <row r="693" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="693" spans="71:71">
       <c r="BS693" s="1" t="s">
         <v>2006</v>
       </c>
     </row>
-    <row r="694" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="694" spans="71:71">
       <c r="BS694" s="1" t="s">
         <v>2007</v>
       </c>
     </row>
-    <row r="695" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="695" spans="71:71">
       <c r="BS695" s="1" t="s">
         <v>2008</v>
       </c>
     </row>
-    <row r="696" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="696" spans="71:71">
       <c r="BS696" s="1" t="s">
         <v>2009</v>
       </c>
     </row>
-    <row r="697" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="697" spans="71:71">
       <c r="BS697" s="1" t="s">
         <v>2010</v>
       </c>
     </row>
-    <row r="698" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="698" spans="71:71">
       <c r="BS698" s="1" t="s">
         <v>2011</v>
       </c>
     </row>
-    <row r="699" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="699" spans="71:71">
       <c r="BS699" s="1" t="s">
         <v>2012</v>
       </c>
     </row>
-    <row r="700" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="700" spans="71:71">
       <c r="BS700" s="1" t="s">
         <v>2013</v>
       </c>
     </row>
-    <row r="701" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="701" spans="71:71">
       <c r="BS701" s="1" t="s">
         <v>2014</v>
       </c>
     </row>
-    <row r="702" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="702" spans="71:71">
       <c r="BS702" s="1" t="s">
         <v>2015</v>
       </c>
     </row>
-    <row r="703" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="703" spans="71:71">
       <c r="BS703" s="1" t="s">
         <v>2016</v>
       </c>
     </row>
-    <row r="704" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="704" spans="71:71">
       <c r="BS704" s="1" t="s">
         <v>2017</v>
       </c>
     </row>
-    <row r="705" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="705" spans="71:71">
       <c r="BS705" s="1" t="s">
         <v>2018</v>
       </c>
     </row>
-    <row r="706" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="706" spans="71:71">
       <c r="BS706" s="1" t="s">
         <v>2019</v>
       </c>
     </row>
-    <row r="707" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="707" spans="71:71">
       <c r="BS707" s="1" t="s">
         <v>2020</v>
       </c>
     </row>
-    <row r="708" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="708" spans="71:71">
       <c r="BS708" s="1" t="s">
         <v>2021</v>
       </c>
     </row>
-    <row r="709" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="709" spans="71:71">
       <c r="BS709" s="1" t="s">
         <v>2022</v>
       </c>
     </row>
-    <row r="710" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="710" spans="71:71">
       <c r="BS710" s="1" t="s">
         <v>2023</v>
       </c>
     </row>
-    <row r="711" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="711" spans="71:71">
       <c r="BS711" s="1" t="s">
         <v>2024</v>
       </c>
     </row>
-    <row r="712" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="712" spans="71:71">
       <c r="BS712" s="1" t="s">
         <v>2025</v>
       </c>
     </row>
-    <row r="713" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="713" spans="71:71">
       <c r="BS713" s="1" t="s">
         <v>2026</v>
       </c>
     </row>
-    <row r="714" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="714" spans="71:71">
       <c r="BS714" s="1" t="s">
         <v>2027</v>
       </c>
     </row>
-    <row r="715" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="715" spans="71:71">
       <c r="BS715" s="1" t="s">
         <v>2028</v>
       </c>
     </row>
-    <row r="716" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="716" spans="71:71">
       <c r="BS716" s="1" t="s">
         <v>2029</v>
       </c>
     </row>
-    <row r="717" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="717" spans="71:71">
       <c r="BS717" s="1" t="s">
         <v>2030</v>
       </c>
     </row>
-    <row r="718" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="718" spans="71:71">
       <c r="BS718" s="1" t="s">
         <v>2031</v>
       </c>
     </row>
-    <row r="719" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="719" spans="71:71">
       <c r="BS719" s="1" t="s">
         <v>2032</v>
       </c>
     </row>
-    <row r="720" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="720" spans="71:71">
       <c r="BS720" s="1" t="s">
         <v>2033</v>
       </c>
     </row>
-    <row r="721" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="721" spans="71:71">
       <c r="BS721" s="1" t="s">
         <v>2034</v>
       </c>
     </row>
-    <row r="722" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="722" spans="71:71">
       <c r="BS722" s="1" t="s">
         <v>2035</v>
       </c>
     </row>
-    <row r="723" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="723" spans="71:71">
       <c r="BS723" s="1" t="s">
         <v>2036</v>
       </c>
     </row>
-    <row r="724" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="724" spans="71:71">
       <c r="BS724" s="1" t="s">
         <v>2037</v>
       </c>
     </row>
-    <row r="725" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="725" spans="71:71">
       <c r="BS725" s="1" t="s">
         <v>2038</v>
       </c>
     </row>
-    <row r="726" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="726" spans="71:71">
       <c r="BS726" s="1" t="s">
         <v>2039</v>
       </c>
     </row>
-    <row r="727" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="727" spans="71:71">
       <c r="BS727" s="1" t="s">
         <v>2040</v>
       </c>
     </row>
-    <row r="728" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="728" spans="71:71">
       <c r="BS728" s="1" t="s">
         <v>2041</v>
       </c>
     </row>
-    <row r="729" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="729" spans="71:71">
       <c r="BS729" s="1" t="s">
         <v>2042</v>
       </c>
     </row>
-    <row r="730" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="730" spans="71:71">
       <c r="BS730" s="1" t="s">
         <v>2043</v>
       </c>
     </row>
-    <row r="731" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="731" spans="71:71">
       <c r="BS731" s="1" t="s">
         <v>2044</v>
       </c>
     </row>
-    <row r="732" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="732" spans="71:71">
       <c r="BS732" s="1" t="s">
         <v>2045</v>
       </c>
     </row>
-    <row r="733" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="733" spans="71:71">
       <c r="BS733" s="1" t="s">
         <v>2046</v>
       </c>
     </row>
-    <row r="734" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="734" spans="71:71">
       <c r="BS734" s="1" t="s">
         <v>2047</v>
       </c>
     </row>
-    <row r="735" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="735" spans="71:71">
       <c r="BS735" s="1" t="s">
         <v>2048</v>
       </c>
     </row>
-    <row r="736" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="736" spans="71:71">
       <c r="BS736" s="1" t="s">
         <v>2049</v>
       </c>
     </row>
-    <row r="737" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="737" spans="71:71">
       <c r="BS737" s="1" t="s">
         <v>2050</v>
       </c>
     </row>
-    <row r="738" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="738" spans="71:71">
       <c r="BS738" s="1" t="s">
         <v>2051</v>
       </c>
     </row>
-    <row r="739" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="739" spans="71:71">
       <c r="BS739" s="1" t="s">
         <v>2052</v>
       </c>
     </row>
-    <row r="740" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="740" spans="71:71">
       <c r="BS740" s="1" t="s">
         <v>2053</v>
       </c>
     </row>
-    <row r="741" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="741" spans="71:71">
       <c r="BS741" s="1" t="s">
         <v>2054</v>
       </c>
     </row>
-    <row r="742" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="742" spans="71:71">
       <c r="BS742" s="1" t="s">
         <v>2055</v>
       </c>
     </row>
-    <row r="743" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="743" spans="71:71">
       <c r="BS743" s="1" t="s">
         <v>2056</v>
       </c>
     </row>
-    <row r="744" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="744" spans="71:71">
       <c r="BS744" s="1" t="s">
         <v>2057</v>
       </c>
     </row>
-    <row r="745" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="745" spans="71:71">
       <c r="BS745" s="1" t="s">
         <v>2058</v>
       </c>
     </row>
-    <row r="746" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="746" spans="71:71">
       <c r="BS746" s="1" t="s">
         <v>2059</v>
       </c>
     </row>
-    <row r="747" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="747" spans="71:71">
       <c r="BS747" s="1" t="s">
         <v>2060</v>
       </c>
     </row>
-    <row r="748" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="748" spans="71:71">
       <c r="BS748" s="1" t="s">
         <v>2061</v>
       </c>
     </row>
-    <row r="749" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="749" spans="71:71">
       <c r="BS749" s="1" t="s">
         <v>2062</v>
       </c>
     </row>
-    <row r="750" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="750" spans="71:71">
       <c r="BS750" s="1" t="s">
         <v>2063</v>
       </c>
     </row>
-    <row r="751" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="751" spans="71:71">
       <c r="BS751" s="1" t="s">
         <v>2064</v>
       </c>
     </row>
-    <row r="752" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="752" spans="71:71">
       <c r="BS752" s="1" t="s">
         <v>2065</v>
       </c>
     </row>
-    <row r="753" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="753" spans="71:71">
       <c r="BS753" s="1" t="s">
         <v>2066</v>
       </c>
     </row>
-    <row r="754" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="754" spans="71:71">
       <c r="BS754" s="1" t="s">
         <v>2067</v>
       </c>
     </row>
-    <row r="755" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="755" spans="71:71">
       <c r="BS755" s="1" t="s">
         <v>2068</v>
       </c>
     </row>
-    <row r="756" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="756" spans="71:71">
       <c r="BS756" s="1" t="s">
         <v>2069</v>
       </c>
     </row>
-    <row r="757" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="757" spans="71:71">
       <c r="BS757" s="1" t="s">
         <v>2070</v>
       </c>
     </row>
-    <row r="758" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="758" spans="71:71">
       <c r="BS758" s="1" t="s">
         <v>2071</v>
       </c>
     </row>
-    <row r="759" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="759" spans="71:71">
       <c r="BS759" s="1" t="s">
         <v>2072</v>
       </c>
     </row>
-    <row r="760" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="760" spans="71:71">
       <c r="BS760" s="1" t="s">
         <v>2073</v>
       </c>
     </row>
-    <row r="761" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="761" spans="71:71">
       <c r="BS761" s="1" t="s">
         <v>2074</v>
       </c>
     </row>
-    <row r="762" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="762" spans="71:71">
       <c r="BS762" s="1" t="s">
         <v>2075</v>
       </c>
     </row>
-    <row r="763" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="763" spans="71:71">
       <c r="BS763" s="1" t="s">
         <v>2076</v>
       </c>
     </row>
-    <row r="764" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="764" spans="71:71">
       <c r="BS764" s="1" t="s">
         <v>2077</v>
       </c>
     </row>
-    <row r="765" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="765" spans="71:71">
       <c r="BS765" s="1" t="s">
         <v>2078</v>
       </c>
     </row>
-    <row r="766" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="766" spans="71:71">
       <c r="BS766" s="1" t="s">
         <v>2079</v>
       </c>
     </row>
-    <row r="767" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="767" spans="71:71">
       <c r="BS767" s="1" t="s">
         <v>2080</v>
       </c>
     </row>
-    <row r="768" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="768" spans="71:71">
       <c r="BS768" s="1" t="s">
         <v>2081</v>
       </c>
     </row>
-    <row r="769" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="769" spans="71:71">
       <c r="BS769" s="1" t="s">
         <v>2082</v>
       </c>
     </row>
-    <row r="770" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="770" spans="71:71">
       <c r="BS770" s="1" t="s">
         <v>2083</v>
       </c>
     </row>
-    <row r="771" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="771" spans="71:71">
       <c r="BS771" s="1" t="s">
         <v>2084</v>
       </c>
     </row>
-    <row r="772" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="772" spans="71:71">
       <c r="BS772" s="1" t="s">
         <v>2085</v>
       </c>
     </row>
-    <row r="773" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="773" spans="71:71">
       <c r="BS773" s="1" t="s">
         <v>2086</v>
       </c>
     </row>
-    <row r="774" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="774" spans="71:71">
       <c r="BS774" s="1" t="s">
         <v>2087</v>
       </c>
     </row>
-    <row r="775" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="775" spans="71:71">
       <c r="BS775" s="1" t="s">
         <v>2088</v>
       </c>
     </row>
-    <row r="776" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="776" spans="71:71">
       <c r="BS776" s="1" t="s">
         <v>2089</v>
       </c>
     </row>
-    <row r="777" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="777" spans="71:71">
       <c r="BS777" s="1" t="s">
         <v>2090</v>
       </c>
     </row>
-    <row r="778" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="778" spans="71:71">
       <c r="BS778" s="1" t="s">
         <v>2091</v>
       </c>
     </row>
-    <row r="779" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="779" spans="71:71">
       <c r="BS779" s="1" t="s">
         <v>2092</v>
       </c>
     </row>
-    <row r="780" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="780" spans="71:71">
       <c r="BS780" s="1" t="s">
         <v>2093</v>
       </c>
     </row>
-    <row r="781" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="781" spans="71:71">
       <c r="BS781" s="1" t="s">
         <v>2094</v>
       </c>
     </row>
-    <row r="782" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="782" spans="71:71">
       <c r="BS782" s="1" t="s">
         <v>2095</v>
       </c>
     </row>
-    <row r="783" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="783" spans="71:71">
       <c r="BS783" s="1" t="s">
         <v>2096</v>
       </c>
     </row>
-    <row r="784" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="784" spans="71:71">
       <c r="BS784" s="1" t="s">
         <v>2097</v>
       </c>
     </row>
-    <row r="785" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="785" spans="71:71">
       <c r="BS785" s="1" t="s">
         <v>2098</v>
       </c>
     </row>
-    <row r="786" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="786" spans="71:71">
       <c r="BS786" s="1" t="s">
         <v>2099</v>
       </c>
     </row>
-    <row r="787" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="787" spans="71:71">
       <c r="BS787" s="1" t="s">
         <v>2100</v>
       </c>
     </row>
-    <row r="788" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="788" spans="71:71">
       <c r="BS788" s="1" t="s">
         <v>2101</v>
       </c>
     </row>
-    <row r="789" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="789" spans="71:71">
       <c r="BS789" s="1" t="s">
         <v>2102</v>
       </c>
     </row>
-    <row r="790" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="790" spans="71:71">
       <c r="BS790" s="1" t="s">
         <v>2103</v>
       </c>
     </row>
-    <row r="791" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="791" spans="71:71">
       <c r="BS791" s="1" t="s">
         <v>2104</v>
       </c>
     </row>
-    <row r="792" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="792" spans="71:71">
       <c r="BS792" s="1" t="s">
         <v>2105</v>
       </c>
     </row>
-    <row r="793" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="793" spans="71:71">
       <c r="BS793" s="1" t="s">
         <v>2106</v>
       </c>
     </row>
-    <row r="794" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="794" spans="71:71">
       <c r="BS794" s="1" t="s">
         <v>2107</v>
       </c>
     </row>
-    <row r="795" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="795" spans="71:71">
       <c r="BS795" s="1" t="s">
         <v>2108</v>
       </c>
     </row>
-    <row r="796" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="796" spans="71:71">
       <c r="BS796" s="1" t="s">
         <v>2109</v>
       </c>
     </row>
-    <row r="797" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="797" spans="71:71">
       <c r="BS797" s="1" t="s">
         <v>2110</v>
       </c>
     </row>
-    <row r="798" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="798" spans="71:71">
       <c r="BS798" s="1" t="s">
         <v>2111</v>
       </c>
     </row>
-    <row r="799" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="799" spans="71:71">
       <c r="BS799" s="1" t="s">
         <v>2112</v>
       </c>
     </row>
-    <row r="800" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="800" spans="71:71">
       <c r="BS800" s="1" t="s">
         <v>2113</v>
       </c>
     </row>
-    <row r="801" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="801" spans="71:71">
       <c r="BS801" s="1" t="s">
         <v>2114</v>
       </c>
     </row>
-    <row r="802" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="802" spans="71:71">
       <c r="BS802" s="1" t="s">
         <v>2115</v>
       </c>
     </row>
-    <row r="803" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="803" spans="71:71">
       <c r="BS803" s="1" t="s">
         <v>2116</v>
       </c>
     </row>
-    <row r="804" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="804" spans="71:71">
       <c r="BS804" s="1" t="s">
         <v>2117</v>
       </c>
     </row>
-    <row r="805" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="805" spans="71:71">
       <c r="BS805" s="1" t="s">
         <v>2118</v>
       </c>
     </row>
-    <row r="806" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="806" spans="71:71">
       <c r="BS806" s="1" t="s">
         <v>2119</v>
       </c>
     </row>
-    <row r="807" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="807" spans="71:71">
       <c r="BS807" s="1" t="s">
         <v>2120</v>
       </c>
     </row>
-    <row r="808" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="808" spans="71:71">
       <c r="BS808" s="1" t="s">
         <v>2121</v>
       </c>
     </row>
-    <row r="809" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="809" spans="71:71">
       <c r="BS809" s="1" t="s">
         <v>2122</v>
       </c>
     </row>
-    <row r="810" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="810" spans="71:71">
       <c r="BS810" s="1" t="s">
         <v>2123</v>
       </c>
     </row>
-    <row r="811" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="811" spans="71:71">
       <c r="BS811" s="1" t="s">
         <v>2124</v>
       </c>
     </row>
-    <row r="812" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="812" spans="71:71">
       <c r="BS812" s="1" t="s">
         <v>2125</v>
       </c>
     </row>
-    <row r="813" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="813" spans="71:71">
       <c r="BS813" s="1" t="s">
         <v>2126</v>
       </c>
     </row>
-    <row r="814" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="814" spans="71:71">
       <c r="BS814" s="1" t="s">
         <v>2127</v>
       </c>
     </row>
-    <row r="815" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="815" spans="71:71">
       <c r="BS815" s="1" t="s">
         <v>2128</v>
       </c>
     </row>
-    <row r="816" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="816" spans="71:71">
       <c r="BS816" s="1" t="s">
         <v>2129</v>
       </c>
     </row>
-    <row r="817" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="817" spans="71:71">
       <c r="BS817" s="1" t="s">
         <v>2130</v>
       </c>
     </row>
-    <row r="818" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="818" spans="71:71">
       <c r="BS818" s="1" t="s">
         <v>2131</v>
       </c>
     </row>
-    <row r="819" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="819" spans="71:71">
       <c r="BS819" s="1" t="s">
         <v>2132</v>
       </c>
     </row>
-    <row r="820" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="820" spans="71:71">
       <c r="BS820" s="1" t="s">
         <v>2133</v>
       </c>
     </row>
-    <row r="821" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="821" spans="71:71">
       <c r="BS821" s="1" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="822" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="822" spans="71:71">
       <c r="BS822" s="1" t="s">
         <v>2135</v>
       </c>
     </row>
-    <row r="823" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="823" spans="71:71">
       <c r="BS823" s="1" t="s">
         <v>2136</v>
       </c>
     </row>
-    <row r="824" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="824" spans="71:71">
       <c r="BS824" s="1" t="s">
         <v>2137</v>
       </c>
     </row>
-    <row r="825" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="825" spans="71:71">
       <c r="BS825" s="1" t="s">
         <v>2138</v>
       </c>
     </row>
-    <row r="826" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="826" spans="71:71">
       <c r="BS826" s="1" t="s">
         <v>2139</v>
       </c>
     </row>
-    <row r="827" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="827" spans="71:71">
       <c r="BS827" s="1" t="s">
         <v>2140</v>
       </c>
     </row>
-    <row r="828" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="828" spans="71:71">
       <c r="BS828" s="1" t="s">
         <v>2141</v>
       </c>
     </row>
-    <row r="829" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="829" spans="71:71">
       <c r="BS829" s="1" t="s">
         <v>2142</v>
       </c>
     </row>
-    <row r="830" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="830" spans="71:71">
       <c r="BS830" s="1" t="s">
         <v>2143</v>
       </c>
     </row>
-    <row r="831" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="831" spans="71:71">
       <c r="BS831" s="1" t="s">
         <v>2144</v>
       </c>
     </row>
-    <row r="832" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="832" spans="71:71">
       <c r="BS832" s="1" t="s">
         <v>2145</v>
       </c>
     </row>
-    <row r="833" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="833" spans="71:71">
       <c r="BS833" s="1" t="s">
         <v>2146</v>
       </c>
     </row>
-    <row r="834" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="834" spans="71:71">
       <c r="BS834" s="1" t="s">
         <v>2147</v>
       </c>
     </row>
-    <row r="835" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="835" spans="71:71">
       <c r="BS835" s="1" t="s">
         <v>2148</v>
       </c>
     </row>
-    <row r="836" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="836" spans="71:71">
       <c r="BS836" s="1" t="s">
         <v>2149</v>
       </c>
     </row>
-    <row r="837" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="837" spans="71:71">
       <c r="BS837" s="1" t="s">
         <v>2150</v>
       </c>
     </row>
-    <row r="838" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="838" spans="71:71">
       <c r="BS838" s="1" t="s">
         <v>2151</v>
       </c>
     </row>
-    <row r="839" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="839" spans="71:71">
       <c r="BS839" s="1" t="s">
         <v>2152</v>
       </c>
     </row>
-    <row r="840" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="840" spans="71:71">
       <c r="BS840" s="1" t="s">
         <v>2153</v>
       </c>
     </row>
-    <row r="841" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="841" spans="71:71">
       <c r="BS841" s="1" t="s">
         <v>2154</v>
       </c>
     </row>
-    <row r="842" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="842" spans="71:71">
       <c r="BS842" s="1" t="s">
         <v>2155</v>
       </c>
     </row>
-    <row r="843" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="843" spans="71:71">
       <c r="BS843" s="1" t="s">
         <v>2156</v>
       </c>
     </row>
-    <row r="844" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="844" spans="71:71">
       <c r="BS844" s="1" t="s">
         <v>2157</v>
       </c>
     </row>
-    <row r="845" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="845" spans="71:71">
       <c r="BS845" s="1" t="s">
         <v>2158</v>
       </c>
     </row>
-    <row r="846" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="846" spans="71:71">
       <c r="BS846" s="1" t="s">
         <v>2159</v>
       </c>
     </row>
-    <row r="847" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="847" spans="71:71">
       <c r="BS847" s="1" t="s">
         <v>2160</v>
       </c>
     </row>
-    <row r="848" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="848" spans="71:71">
       <c r="BS848" s="1" t="s">
         <v>2161</v>
       </c>
     </row>
-    <row r="849" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="849" spans="71:71">
       <c r="BS849" s="1" t="s">
         <v>2162</v>
       </c>
     </row>
-    <row r="850" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="850" spans="71:71">
       <c r="BS850" s="1" t="s">
         <v>2163</v>
       </c>
     </row>
-    <row r="851" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="851" spans="71:71">
       <c r="BS851" s="1" t="s">
         <v>2164</v>
       </c>
     </row>
-    <row r="852" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="852" spans="71:71">
       <c r="BS852" s="1" t="s">
         <v>2165</v>
       </c>
     </row>
-    <row r="853" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="853" spans="71:71">
       <c r="BS853" s="1" t="s">
         <v>2166</v>
       </c>
     </row>
-    <row r="854" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="854" spans="71:71">
       <c r="BS854" s="1" t="s">
         <v>2167</v>
       </c>
     </row>
-    <row r="855" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="855" spans="71:71">
       <c r="BS855" s="1" t="s">
         <v>2168</v>
       </c>
     </row>
-    <row r="856" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="856" spans="71:71">
       <c r="BS856" s="1" t="s">
         <v>2169</v>
       </c>
     </row>
-    <row r="857" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="857" spans="71:71">
       <c r="BS857" s="1" t="s">
         <v>2170</v>
       </c>
     </row>
-    <row r="858" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="858" spans="71:71">
       <c r="BS858" s="1" t="s">
         <v>2171</v>
       </c>
     </row>
-    <row r="859" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="859" spans="71:71">
       <c r="BS859" s="1" t="s">
         <v>2172</v>
       </c>
     </row>
-    <row r="860" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="860" spans="71:71">
       <c r="BS860" s="1" t="s">
         <v>2173</v>
       </c>
     </row>
-    <row r="861" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="861" spans="71:71">
       <c r="BS861" s="1" t="s">
         <v>2174</v>
       </c>
     </row>
-    <row r="862" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="862" spans="71:71">
       <c r="BS862" s="1" t="s">
         <v>2175</v>
       </c>
     </row>
-    <row r="863" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="863" spans="71:71">
       <c r="BS863" s="1" t="s">
         <v>2176</v>
       </c>
     </row>
-    <row r="864" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="864" spans="71:71">
       <c r="BS864" s="1" t="s">
         <v>2177</v>
       </c>
     </row>
-    <row r="865" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="865" spans="71:71">
       <c r="BS865" s="1" t="s">
         <v>2178</v>
       </c>
     </row>
-    <row r="866" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="866" spans="71:71">
       <c r="BS866" s="1" t="s">
         <v>2179</v>
       </c>
     </row>
-    <row r="867" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="867" spans="71:71">
       <c r="BS867" s="1" t="s">
         <v>2180</v>
       </c>
     </row>
-    <row r="868" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="868" spans="71:71">
       <c r="BS868" s="1" t="s">
         <v>2181</v>
       </c>
     </row>
-    <row r="869" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="869" spans="71:71">
       <c r="BS869" s="1" t="s">
         <v>2182</v>
       </c>
     </row>
-    <row r="870" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="870" spans="71:71">
       <c r="BS870" s="1" t="s">
         <v>2183</v>
       </c>
     </row>
-    <row r="871" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="871" spans="71:71">
       <c r="BS871" s="1" t="s">
         <v>2184</v>
       </c>
     </row>
-    <row r="872" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="872" spans="71:71">
       <c r="BS872" s="1" t="s">
         <v>2185</v>
       </c>
     </row>
-    <row r="873" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="873" spans="71:71">
       <c r="BS873" s="1" t="s">
         <v>2186</v>
       </c>
     </row>
-    <row r="874" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="874" spans="71:71">
       <c r="BS874" s="1" t="s">
         <v>2187</v>
       </c>
     </row>
-    <row r="875" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="875" spans="71:71">
       <c r="BS875" s="1" t="s">
         <v>2188</v>
       </c>
     </row>
-    <row r="876" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="876" spans="71:71">
       <c r="BS876" s="1" t="s">
         <v>2189</v>
       </c>
     </row>
-    <row r="877" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="877" spans="71:71">
       <c r="BS877" s="1" t="s">
         <v>2190</v>
       </c>
     </row>
-    <row r="878" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="878" spans="71:71">
       <c r="BS878" s="1" t="s">
         <v>2191</v>
       </c>
     </row>
-    <row r="879" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="879" spans="71:71">
       <c r="BS879" s="1" t="s">
         <v>2192</v>
       </c>
     </row>
-    <row r="880" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="880" spans="71:71">
       <c r="BS880" s="1" t="s">
         <v>2193</v>
       </c>
     </row>
-    <row r="881" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="881" spans="71:71">
       <c r="BS881" s="1" t="s">
         <v>2194</v>
       </c>
     </row>
-    <row r="882" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="882" spans="71:71">
       <c r="BS882" s="1" t="s">
         <v>2195</v>
       </c>
     </row>
-    <row r="883" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="883" spans="71:71">
       <c r="BS883" s="1" t="s">
         <v>2196</v>
       </c>
     </row>
-    <row r="884" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="884" spans="71:71">
       <c r="BS884" s="1" t="s">
         <v>2197</v>
       </c>
     </row>
-    <row r="885" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="885" spans="71:71">
       <c r="BS885" s="1" t="s">
         <v>2198</v>
       </c>
     </row>
-    <row r="886" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="886" spans="71:71">
       <c r="BS886" s="1" t="s">
         <v>2199</v>
       </c>
     </row>
-    <row r="887" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="887" spans="71:71">
       <c r="BS887" s="1" t="s">
         <v>2200</v>
       </c>
     </row>
-    <row r="888" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="888" spans="71:71">
       <c r="BS888" s="1" t="s">
         <v>2201</v>
       </c>
     </row>
-    <row r="889" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="889" spans="71:71">
       <c r="BS889" s="1" t="s">
         <v>2202</v>
       </c>
     </row>
-    <row r="890" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="890" spans="71:71">
       <c r="BS890" s="1" t="s">
         <v>2203</v>
       </c>
     </row>
-    <row r="891" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="891" spans="71:71">
       <c r="BS891" s="1" t="s">
         <v>2204</v>
       </c>
     </row>
-    <row r="892" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="892" spans="71:71">
       <c r="BS892" s="1" t="s">
         <v>2205</v>
       </c>
     </row>
-    <row r="893" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="893" spans="71:71">
       <c r="BS893" s="1" t="s">
         <v>2206</v>
       </c>
     </row>
-    <row r="894" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="894" spans="71:71">
       <c r="BS894" s="1" t="s">
         <v>2207</v>
       </c>
     </row>
-    <row r="895" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="895" spans="71:71">
       <c r="BS895" s="1" t="s">
         <v>2208</v>
       </c>
     </row>
-    <row r="896" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="896" spans="71:71">
       <c r="BS896" s="1" t="s">
         <v>2209</v>
       </c>
     </row>
-    <row r="897" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="897" spans="71:71">
       <c r="BS897" s="1" t="s">
         <v>2210</v>
       </c>
     </row>
-    <row r="898" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="898" spans="71:71">
       <c r="BS898" s="1" t="s">
         <v>2211</v>
       </c>
     </row>
-    <row r="899" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="899" spans="71:71">
       <c r="BS899" s="1" t="s">
         <v>2212</v>
       </c>
     </row>
-    <row r="900" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="900" spans="71:71">
       <c r="BS900" s="1" t="s">
         <v>2213</v>
       </c>
     </row>
-    <row r="901" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="901" spans="71:71">
       <c r="BS901" s="1" t="s">
         <v>2214</v>
       </c>
     </row>
-    <row r="902" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="902" spans="71:71">
       <c r="BS902" s="1" t="s">
         <v>2215</v>
       </c>
     </row>
-    <row r="903" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="903" spans="71:71">
       <c r="BS903" s="1" t="s">
         <v>2216</v>
       </c>
     </row>
-    <row r="904" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="904" spans="71:71">
       <c r="BS904" s="1" t="s">
         <v>2217</v>
       </c>
     </row>
-    <row r="905" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="905" spans="71:71">
       <c r="BS905" s="1" t="s">
         <v>2218</v>
       </c>
     </row>
-    <row r="906" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="906" spans="71:71">
       <c r="BS906" s="1" t="s">
         <v>2219</v>
       </c>
     </row>
-    <row r="907" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="907" spans="71:71">
       <c r="BS907" s="1" t="s">
         <v>2220</v>
       </c>
     </row>
-    <row r="908" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="908" spans="71:71">
       <c r="BS908" s="1" t="s">
         <v>2221</v>
       </c>
     </row>
-    <row r="909" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="909" spans="71:71">
       <c r="BS909" s="1" t="s">
         <v>2222</v>
       </c>
     </row>
-    <row r="910" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="910" spans="71:71">
       <c r="BS910" s="1" t="s">
         <v>2223</v>
       </c>
     </row>
-    <row r="911" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="911" spans="71:71">
       <c r="BS911" s="1" t="s">
         <v>2224</v>
       </c>
     </row>
-    <row r="912" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="912" spans="71:71">
       <c r="BS912" s="1" t="s">
         <v>2225</v>
       </c>
     </row>
-    <row r="913" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="913" spans="71:71">
       <c r="BS913" s="1" t="s">
         <v>2226</v>
       </c>
     </row>
-    <row r="914" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="914" spans="71:71">
       <c r="BS914" s="1" t="s">
         <v>2227</v>
       </c>
     </row>
-    <row r="915" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="915" spans="71:71">
       <c r="BS915" s="1" t="s">
         <v>2228</v>
       </c>
     </row>
-    <row r="916" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="916" spans="71:71">
       <c r="BS916" s="1" t="s">
         <v>2229</v>
       </c>
     </row>
-    <row r="917" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="917" spans="71:71">
       <c r="BS917" s="1" t="s">
         <v>2230</v>
       </c>
     </row>
-    <row r="918" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="918" spans="71:71">
       <c r="BS918" s="1" t="s">
         <v>2231</v>
       </c>
     </row>
-    <row r="919" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="919" spans="71:71">
       <c r="BS919" s="1" t="s">
         <v>2232</v>
       </c>
     </row>
-    <row r="920" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="920" spans="71:71">
       <c r="BS920" s="1" t="s">
         <v>2233</v>
       </c>
     </row>
-    <row r="921" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="921" spans="71:71">
       <c r="BS921" s="1" t="s">
         <v>2234</v>
       </c>
     </row>
-    <row r="922" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="922" spans="71:71">
       <c r="BS922" s="1" t="s">
         <v>2235</v>
       </c>
     </row>
-    <row r="923" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="923" spans="71:71">
       <c r="BS923" s="1" t="s">
         <v>2236</v>
       </c>
     </row>
-    <row r="924" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="924" spans="71:71">
       <c r="BS924" s="1" t="s">
         <v>2237</v>
       </c>
     </row>
-    <row r="925" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="925" spans="71:71">
       <c r="BS925" s="1" t="s">
         <v>2238</v>
       </c>
     </row>
-    <row r="926" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="926" spans="71:71">
       <c r="BS926" s="1" t="s">
         <v>2239</v>
       </c>
     </row>
-    <row r="927" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="927" spans="71:71">
       <c r="BS927" s="1" t="s">
         <v>2240</v>
       </c>
     </row>
-    <row r="928" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="928" spans="71:71">
       <c r="BS928" s="1" t="s">
         <v>2241</v>
       </c>
     </row>
-    <row r="929" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="929" spans="71:71">
       <c r="BS929" s="1" t="s">
         <v>2242</v>
       </c>
     </row>
-    <row r="930" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="930" spans="71:71">
       <c r="BS930" s="1" t="s">
         <v>2243</v>
       </c>
     </row>
-    <row r="931" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="931" spans="71:71">
       <c r="BS931" s="1" t="s">
         <v>2244</v>
       </c>
     </row>
-    <row r="932" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="932" spans="71:71">
       <c r="BS932" s="1" t="s">
         <v>2245</v>
       </c>
     </row>
-    <row r="933" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="933" spans="71:71">
       <c r="BS933" s="1" t="s">
         <v>2246</v>
       </c>
     </row>
-    <row r="934" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="934" spans="71:71">
       <c r="BS934" s="1" t="s">
         <v>2247</v>
       </c>
     </row>
-    <row r="935" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="935" spans="71:71">
       <c r="BS935" s="1" t="s">
         <v>2248</v>
       </c>
     </row>
-    <row r="936" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="936" spans="71:71">
       <c r="BS936" s="1" t="s">
         <v>2249</v>
       </c>
     </row>
-    <row r="937" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="937" spans="71:71">
       <c r="BS937" s="1" t="s">
         <v>2250</v>
       </c>
     </row>
-    <row r="938" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="938" spans="71:71">
       <c r="BS938" s="1" t="s">
         <v>2251</v>
       </c>
     </row>
-    <row r="939" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="939" spans="71:71">
       <c r="BS939" s="1" t="s">
         <v>2252</v>
       </c>
     </row>
-    <row r="940" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="940" spans="71:71">
       <c r="BS940" s="1" t="s">
         <v>2253</v>
       </c>
     </row>
-    <row r="941" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="941" spans="71:71">
       <c r="BS941" s="1" t="s">
         <v>2254</v>
       </c>
     </row>
-    <row r="942" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="942" spans="71:71">
       <c r="BS942" s="1" t="s">
         <v>2255</v>
       </c>
     </row>
-    <row r="943" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="943" spans="71:71">
       <c r="BS943" s="1" t="s">
         <v>2256</v>
       </c>
     </row>
-    <row r="944" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="944" spans="71:71">
       <c r="BS944" s="1" t="s">
         <v>2257</v>
       </c>
     </row>
-    <row r="945" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="945" spans="71:71">
       <c r="BS945" s="1" t="s">
         <v>2258</v>
       </c>
     </row>
-    <row r="946" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="946" spans="71:71">
       <c r="BS946" s="1" t="s">
         <v>2259</v>
       </c>
     </row>
-    <row r="947" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="947" spans="71:71">
       <c r="BS947" s="1" t="s">
         <v>2260</v>
       </c>
     </row>
-    <row r="948" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="948" spans="71:71">
       <c r="BS948" s="1" t="s">
         <v>2261</v>
       </c>
     </row>
-    <row r="949" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="949" spans="71:71">
       <c r="BS949" s="1" t="s">
         <v>2262</v>
       </c>
     </row>
-    <row r="950" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="950" spans="71:71">
       <c r="BS950" s="1" t="s">
         <v>2263</v>
       </c>
     </row>
-    <row r="951" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="951" spans="71:71">
       <c r="BS951" s="1" t="s">
         <v>2264</v>
       </c>
     </row>
-    <row r="952" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="952" spans="71:71">
       <c r="BS952" s="1" t="s">
         <v>2265</v>
       </c>
     </row>
-    <row r="953" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="953" spans="71:71">
       <c r="BS953" s="1" t="s">
         <v>2266</v>
       </c>
     </row>
-    <row r="954" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="954" spans="71:71">
       <c r="BS954" s="1" t="s">
         <v>2267</v>
       </c>
     </row>
-    <row r="955" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="955" spans="71:71">
       <c r="BS955" s="1" t="s">
         <v>2268</v>
       </c>
     </row>
-    <row r="956" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="956" spans="71:71">
       <c r="BS956" s="1" t="s">
         <v>2269</v>
       </c>
     </row>
-    <row r="957" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="957" spans="71:71">
       <c r="BS957" s="1" t="s">
         <v>2270</v>
       </c>
     </row>
-    <row r="958" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="958" spans="71:71">
       <c r="BS958" s="1" t="s">
         <v>2271</v>
       </c>
     </row>
-    <row r="959" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="959" spans="71:71">
       <c r="BS959" s="1" t="s">
         <v>2272</v>
       </c>
     </row>
-    <row r="960" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="960" spans="71:71">
       <c r="BS960" s="1" t="s">
         <v>2273</v>
       </c>
     </row>
-    <row r="961" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="961" spans="71:71">
       <c r="BS961" s="1" t="s">
         <v>2274</v>
       </c>
     </row>
-    <row r="962" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="962" spans="71:71">
       <c r="BS962" s="1" t="s">
         <v>2275</v>
       </c>
     </row>
-    <row r="963" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="963" spans="71:71">
       <c r="BS963" s="1" t="s">
         <v>2276</v>
       </c>
     </row>
-    <row r="964" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="964" spans="71:71">
       <c r="BS964" s="1" t="s">
         <v>2277</v>
       </c>
     </row>
-    <row r="965" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="965" spans="71:71">
       <c r="BS965" s="1" t="s">
         <v>2278</v>
       </c>
     </row>
-    <row r="966" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="966" spans="71:71">
       <c r="BS966" s="1" t="s">
         <v>2279</v>
       </c>
     </row>
-    <row r="967" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="967" spans="71:71">
       <c r="BS967" s="1" t="s">
         <v>2280</v>
       </c>
     </row>
-    <row r="968" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="968" spans="71:71">
       <c r="BS968" s="1" t="s">
         <v>2281</v>
       </c>
     </row>
-    <row r="969" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="969" spans="71:71">
       <c r="BS969" s="1" t="s">
         <v>2282</v>
       </c>
     </row>
-    <row r="970" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="970" spans="71:71">
       <c r="BS970" s="1" t="s">
         <v>2283</v>
       </c>
     </row>
-    <row r="971" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="971" spans="71:71">
       <c r="BS971" s="1" t="s">
         <v>2284</v>
       </c>
     </row>
-    <row r="972" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="972" spans="71:71">
       <c r="BS972" s="1" t="s">
         <v>2285</v>
       </c>
     </row>
-    <row r="973" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="973" spans="71:71">
       <c r="BS973" s="1" t="s">
         <v>2286</v>
       </c>
     </row>
-    <row r="974" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="974" spans="71:71">
       <c r="BS974" s="1" t="s">
         <v>2287</v>
       </c>
     </row>
-    <row r="975" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="975" spans="71:71">
       <c r="BS975" s="1" t="s">
         <v>2288</v>
       </c>
     </row>
-    <row r="976" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="976" spans="71:71">
       <c r="BS976" s="1" t="s">
         <v>2289</v>
       </c>
     </row>
-    <row r="977" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="977" spans="71:71">
       <c r="BS977" s="1" t="s">
         <v>2290</v>
       </c>
     </row>
-    <row r="978" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="978" spans="71:71">
       <c r="BS978" s="1" t="s">
         <v>2291</v>
       </c>
     </row>
-    <row r="979" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="979" spans="71:71">
       <c r="BS979" s="1" t="s">
         <v>2292</v>
       </c>
     </row>
-    <row r="980" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="980" spans="71:71">
       <c r="BS980" s="1" t="s">
         <v>2293</v>
       </c>
     </row>
-    <row r="981" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="981" spans="71:71">
       <c r="BS981" s="1" t="s">
         <v>2294</v>
       </c>
     </row>
-    <row r="982" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="982" spans="71:71">
       <c r="BS982" s="1" t="s">
         <v>2295</v>
       </c>
     </row>
-    <row r="983" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="983" spans="71:71">
       <c r="BS983" s="1" t="s">
         <v>2296</v>
       </c>
     </row>
-    <row r="984" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="984" spans="71:71">
       <c r="BS984" s="1" t="s">
         <v>2297</v>
       </c>
     </row>
-    <row r="985" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="985" spans="71:71">
       <c r="BS985" s="1" t="s">
         <v>2298</v>
       </c>
     </row>
-    <row r="986" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="986" spans="71:71">
       <c r="BS986" s="1" t="s">
         <v>2299</v>
       </c>
     </row>
-    <row r="987" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="987" spans="71:71">
       <c r="BS987" s="1" t="s">
         <v>2300</v>
       </c>
     </row>
-    <row r="988" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="988" spans="71:71">
       <c r="BS988" s="1" t="s">
         <v>2301</v>
       </c>
     </row>
-    <row r="989" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="989" spans="71:71">
       <c r="BS989" s="1" t="s">
         <v>2302</v>
       </c>
     </row>
-    <row r="990" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="990" spans="71:71">
       <c r="BS990" s="1" t="s">
         <v>2303</v>
       </c>
     </row>
-    <row r="991" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="991" spans="71:71">
       <c r="BS991" s="1" t="s">
         <v>2304</v>
       </c>
     </row>
-    <row r="992" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="992" spans="71:71">
       <c r="BS992" s="1" t="s">
         <v>2305</v>
       </c>
     </row>
-    <row r="993" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="993" spans="71:71">
       <c r="BS993" s="1" t="s">
         <v>2306</v>
       </c>
     </row>
-    <row r="994" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="994" spans="71:71">
       <c r="BS994" s="1" t="s">
         <v>2307</v>
       </c>
     </row>
-    <row r="995" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="995" spans="71:71">
       <c r="BS995" s="1" t="s">
         <v>2308</v>
       </c>
     </row>
-    <row r="996" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="996" spans="71:71">
       <c r="BS996" s="1" t="s">
         <v>2309</v>
       </c>
     </row>
-    <row r="997" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="997" spans="71:71">
       <c r="BS997" s="1" t="s">
         <v>2310</v>
       </c>
     </row>
-    <row r="998" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="998" spans="71:71">
       <c r="BS998" s="1" t="s">
         <v>2311</v>
       </c>
     </row>
-    <row r="999" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="999" spans="71:71">
       <c r="BS999" s="1" t="s">
         <v>2312</v>
       </c>
     </row>
-    <row r="1000" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1000" spans="71:71">
       <c r="BS1000" s="1" t="s">
         <v>2313</v>
       </c>
     </row>
-    <row r="1001" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1001" spans="71:71">
       <c r="BS1001" s="1" t="s">
         <v>2314</v>
       </c>
     </row>
-    <row r="1002" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1002" spans="71:71">
       <c r="BS1002" s="1" t="s">
         <v>2315</v>
       </c>
     </row>
-    <row r="1003" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1003" spans="71:71">
       <c r="BS1003" s="1" t="s">
         <v>2316</v>
       </c>
     </row>
-    <row r="1004" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1004" spans="71:71">
       <c r="BS1004" s="1" t="s">
         <v>2317</v>
       </c>
     </row>
-    <row r="1005" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1005" spans="71:71">
       <c r="BS1005" s="1" t="s">
         <v>2318</v>
       </c>
     </row>
-    <row r="1006" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1006" spans="71:71">
       <c r="BS1006" s="1" t="s">
         <v>2319</v>
       </c>
     </row>
-    <row r="1007" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1007" spans="71:71">
       <c r="BS1007" s="1" t="s">
         <v>2320</v>
       </c>
     </row>
-    <row r="1008" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1008" spans="71:71">
       <c r="BS1008" s="1" t="s">
         <v>2321</v>
       </c>
     </row>
-    <row r="1009" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1009" spans="71:71">
       <c r="BS1009" s="1" t="s">
         <v>2322</v>
       </c>
     </row>
-    <row r="1010" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1010" spans="71:71">
       <c r="BS1010" s="1" t="s">
         <v>2323</v>
       </c>
     </row>
-    <row r="1011" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1011" spans="71:71">
       <c r="BS1011" s="1" t="s">
         <v>2324</v>
       </c>
     </row>
-    <row r="1012" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1012" spans="71:71">
       <c r="BS1012" s="1" t="s">
         <v>2325</v>
       </c>
     </row>
-    <row r="1013" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1013" spans="71:71">
       <c r="BS1013" s="1" t="s">
         <v>2326</v>
       </c>
     </row>
-    <row r="1014" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1014" spans="71:71">
       <c r="BS1014" s="1" t="s">
         <v>2327</v>
       </c>
     </row>
-    <row r="1015" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1015" spans="71:71">
       <c r="BS1015" s="1" t="s">
         <v>2328</v>
       </c>
     </row>
-    <row r="1016" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1016" spans="71:71">
       <c r="BS1016" s="1" t="s">
         <v>2329</v>
       </c>
     </row>
-    <row r="1017" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1017" spans="71:71">
       <c r="BS1017" s="1" t="s">
         <v>2330</v>
       </c>
     </row>
-    <row r="1018" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1018" spans="71:71">
       <c r="BS1018" s="1" t="s">
         <v>2331</v>
       </c>
     </row>
-    <row r="1019" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1019" spans="71:71">
       <c r="BS1019" s="1" t="s">
         <v>2332</v>
       </c>
     </row>
-    <row r="1020" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1020" spans="71:71">
       <c r="BS1020" s="1" t="s">
         <v>2333</v>
       </c>
     </row>
-    <row r="1021" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1021" spans="71:71">
       <c r="BS1021" s="1" t="s">
         <v>2334</v>
       </c>
     </row>
-    <row r="1022" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1022" spans="71:71">
       <c r="BS1022" s="1" t="s">
         <v>2335</v>
       </c>
     </row>
-    <row r="1023" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1023" spans="71:71">
       <c r="BS1023" s="1" t="s">
         <v>2336</v>
       </c>
     </row>
-    <row r="1024" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1024" spans="71:71">
       <c r="BS1024" s="1" t="s">
         <v>2337</v>
       </c>
     </row>
-    <row r="1025" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1025" spans="71:71">
       <c r="BS1025" s="1" t="s">
         <v>2338</v>
       </c>
     </row>
-    <row r="1026" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1026" spans="71:71">
       <c r="BS1026" s="1" t="s">
         <v>2339</v>
       </c>
     </row>
-    <row r="1027" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1027" spans="71:71">
       <c r="BS1027" s="1" t="s">
         <v>2340</v>
       </c>
     </row>
-    <row r="1028" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1028" spans="71:71">
       <c r="BS1028" s="1" t="s">
         <v>2341</v>
       </c>
     </row>
-    <row r="1029" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1029" spans="71:71">
       <c r="BS1029" s="1" t="s">
         <v>2342</v>
       </c>
     </row>
-    <row r="1030" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1030" spans="71:71">
       <c r="BS1030" s="1" t="s">
         <v>2343</v>
       </c>
     </row>
-    <row r="1031" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1031" spans="71:71">
       <c r="BS1031" s="1" t="s">
         <v>2344</v>
       </c>
     </row>
-    <row r="1032" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1032" spans="71:71">
       <c r="BS1032" s="1" t="s">
         <v>2345</v>
       </c>
     </row>
-    <row r="1033" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1033" spans="71:71">
       <c r="BS1033" s="1" t="s">
         <v>2346</v>
       </c>
     </row>
-    <row r="1034" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1034" spans="71:71">
       <c r="BS1034" s="1" t="s">
         <v>2347</v>
       </c>
     </row>
-    <row r="1035" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1035" spans="71:71">
       <c r="BS1035" s="1" t="s">
         <v>2348</v>
       </c>
     </row>
-    <row r="1036" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1036" spans="71:71">
       <c r="BS1036" s="1" t="s">
         <v>2349</v>
       </c>
     </row>
-    <row r="1037" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1037" spans="71:71">
       <c r="BS1037" s="1" t="s">
         <v>2350</v>
       </c>
     </row>
-    <row r="1038" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1038" spans="71:71">
       <c r="BS1038" s="1" t="s">
         <v>2351</v>
       </c>
     </row>
-    <row r="1039" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1039" spans="71:71">
       <c r="BS1039" s="1" t="s">
         <v>2352</v>
       </c>
     </row>
-    <row r="1040" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1040" spans="71:71">
       <c r="BS1040" s="1" t="s">
         <v>2353</v>
       </c>
     </row>
-    <row r="1041" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1041" spans="71:71">
       <c r="BS1041" s="1" t="s">
         <v>2354</v>
       </c>
     </row>
-    <row r="1042" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1042" spans="71:71">
       <c r="BS1042" s="1" t="s">
         <v>2355</v>
       </c>
     </row>
-    <row r="1043" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1043" spans="71:71">
       <c r="BS1043" s="1" t="s">
         <v>2356</v>
       </c>
     </row>
-    <row r="1044" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1044" spans="71:71">
       <c r="BS1044" s="1" t="s">
         <v>2357</v>
       </c>
     </row>
-    <row r="1045" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1045" spans="71:71">
       <c r="BS1045" s="1" t="s">
         <v>2358</v>
       </c>
     </row>
-    <row r="1046" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1046" spans="71:71">
       <c r="BS1046" s="1" t="s">
         <v>2359</v>
       </c>
     </row>
-    <row r="1047" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1047" spans="71:71">
       <c r="BS1047" s="1" t="s">
         <v>2360</v>
       </c>
     </row>
-    <row r="1048" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1048" spans="71:71">
       <c r="BS1048" s="1" t="s">
         <v>2361</v>
       </c>
     </row>
-    <row r="1049" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1049" spans="71:71">
       <c r="BS1049" s="1" t="s">
         <v>2362</v>
       </c>
     </row>
-    <row r="1050" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1050" spans="71:71">
       <c r="BS1050" s="1" t="s">
         <v>2363</v>
       </c>
     </row>
-    <row r="1051" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1051" spans="71:71">
       <c r="BS1051" s="1" t="s">
         <v>2364</v>
       </c>
     </row>
-    <row r="1052" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1052" spans="71:71">
       <c r="BS1052" s="1" t="s">
         <v>2365</v>
       </c>
     </row>
-    <row r="1053" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1053" spans="71:71">
       <c r="BS1053" s="1" t="s">
         <v>2366</v>
       </c>
     </row>
-    <row r="1054" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1054" spans="71:71">
       <c r="BS1054" s="1" t="s">
         <v>2367</v>
       </c>
     </row>
-    <row r="1055" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1055" spans="71:71">
       <c r="BS1055" s="1" t="s">
         <v>2368</v>
       </c>
     </row>
-    <row r="1056" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1056" spans="71:71">
       <c r="BS1056" s="1" t="s">
         <v>2369</v>
       </c>
     </row>
-    <row r="1057" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1057" spans="71:71">
       <c r="BS1057" s="1" t="s">
         <v>2370</v>
       </c>
     </row>
-    <row r="1058" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1058" spans="71:71">
       <c r="BS1058" s="1" t="s">
         <v>2371</v>
       </c>
     </row>
-    <row r="1059" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1059" spans="71:71">
       <c r="BS1059" s="1" t="s">
         <v>2372</v>
       </c>
     </row>
-    <row r="1060" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1060" spans="71:71">
       <c r="BS1060" s="1" t="s">
         <v>2373</v>
       </c>
     </row>
-    <row r="1061" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1061" spans="71:71">
       <c r="BS1061" s="1" t="s">
         <v>2374</v>
       </c>
     </row>
-    <row r="1062" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1062" spans="71:71">
       <c r="BS1062" s="1" t="s">
         <v>2375</v>
       </c>
     </row>
-    <row r="1063" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1063" spans="71:71">
       <c r="BS1063" s="1" t="s">
         <v>2376</v>
       </c>
     </row>
-    <row r="1064" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1064" spans="71:71">
       <c r="BS1064" s="1" t="s">
         <v>2377</v>
       </c>
     </row>
-    <row r="1065" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1065" spans="71:71">
       <c r="BS1065" s="1" t="s">
         <v>2378</v>
       </c>
     </row>
-    <row r="1066" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1066" spans="71:71">
       <c r="BS1066" s="1" t="s">
         <v>2379</v>
       </c>
     </row>
-    <row r="1067" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1067" spans="71:71">
       <c r="BS1067" s="1" t="s">
         <v>2380</v>
       </c>
     </row>
-    <row r="1068" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1068" spans="71:71">
       <c r="BS1068" s="1" t="s">
         <v>2381</v>
       </c>
     </row>
-    <row r="1069" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1069" spans="71:71">
       <c r="BS1069" s="1" t="s">
         <v>2382</v>
       </c>
     </row>
-    <row r="1070" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1070" spans="71:71">
       <c r="BS1070" s="1" t="s">
         <v>2383</v>
       </c>
     </row>
-    <row r="1071" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1071" spans="71:71">
       <c r="BS1071" s="1" t="s">
         <v>2384</v>
       </c>
     </row>
-    <row r="1072" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1072" spans="71:71">
       <c r="BS1072" s="1" t="s">
         <v>2385</v>
       </c>
     </row>
-    <row r="1073" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1073" spans="71:71">
       <c r="BS1073" s="1" t="s">
         <v>2386</v>
       </c>
     </row>
-    <row r="1074" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1074" spans="71:71">
       <c r="BS1074" s="1" t="s">
         <v>2387</v>
       </c>
     </row>
-    <row r="1075" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1075" spans="71:71">
       <c r="BS1075" s="1" t="s">
         <v>2388</v>
       </c>
     </row>
-    <row r="1076" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1076" spans="71:71">
       <c r="BS1076" s="1" t="s">
         <v>2389</v>
       </c>
     </row>
-    <row r="1077" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1077" spans="71:71">
       <c r="BS1077" s="1" t="s">
         <v>2390</v>
       </c>
     </row>
-    <row r="1078" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1078" spans="71:71">
       <c r="BS1078" s="1" t="s">
         <v>2391</v>
       </c>
     </row>
-    <row r="1079" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1079" spans="71:71">
       <c r="BS1079" s="1" t="s">
         <v>2392</v>
       </c>
     </row>
-    <row r="1080" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1080" spans="71:71">
       <c r="BS1080" s="1" t="s">
         <v>2393</v>
       </c>
     </row>
-    <row r="1081" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1081" spans="71:71">
       <c r="BS1081" s="1" t="s">
         <v>2394</v>
       </c>
     </row>
-    <row r="1082" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1082" spans="71:71">
       <c r="BS1082" s="1" t="s">
         <v>2395</v>
       </c>
     </row>
-    <row r="1083" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1083" spans="71:71">
       <c r="BS1083" s="1" t="s">
         <v>2396</v>
       </c>
     </row>
-    <row r="1084" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1084" spans="71:71">
       <c r="BS1084" s="1" t="s">
         <v>2397</v>
       </c>
     </row>
-    <row r="1085" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1085" spans="71:71">
       <c r="BS1085" s="1" t="s">
         <v>2398</v>
       </c>
     </row>
-    <row r="1086" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1086" spans="71:71">
       <c r="BS1086" s="1" t="s">
         <v>2399</v>
       </c>
     </row>
-    <row r="1087" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1087" spans="71:71">
       <c r="BS1087" s="1" t="s">
         <v>2400</v>
       </c>
     </row>
-    <row r="1088" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1088" spans="71:71">
       <c r="BS1088" s="1" t="s">
         <v>2401</v>
       </c>
     </row>
-    <row r="1089" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1089" spans="71:71">
       <c r="BS1089" s="1" t="s">
         <v>2402</v>
       </c>
     </row>
-    <row r="1090" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1090" spans="71:71">
       <c r="BS1090" s="1" t="s">
         <v>2403</v>
       </c>
     </row>
-    <row r="1091" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1091" spans="71:71">
       <c r="BS1091" s="1" t="s">
         <v>2404</v>
       </c>
     </row>
-    <row r="1092" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1092" spans="71:71">
       <c r="BS1092" s="1" t="s">
         <v>2405</v>
       </c>
     </row>
-    <row r="1093" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1093" spans="71:71">
       <c r="BS1093" s="1" t="s">
         <v>2406</v>
       </c>
     </row>
-    <row r="1094" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1094" spans="71:71">
       <c r="BS1094" s="1" t="s">
         <v>2407</v>
       </c>
     </row>
-    <row r="1095" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1095" spans="71:71">
       <c r="BS1095" s="1" t="s">
         <v>2408</v>
       </c>
     </row>
-    <row r="1096" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1096" spans="71:71">
       <c r="BS1096" s="1" t="s">
         <v>2409</v>
       </c>
     </row>
-    <row r="1097" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1097" spans="71:71">
       <c r="BS1097" s="1" t="s">
         <v>2410</v>
       </c>
     </row>
-    <row r="1098" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1098" spans="71:71">
       <c r="BS1098" s="1" t="s">
         <v>2411</v>
       </c>
     </row>
-    <row r="1099" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1099" spans="71:71">
       <c r="BS1099" s="1" t="s">
         <v>2412</v>
       </c>
     </row>
-    <row r="1100" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1100" spans="71:71">
       <c r="BS1100" s="1" t="s">
         <v>2413</v>
       </c>
     </row>
-    <row r="1101" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1101" spans="71:71">
       <c r="BS1101" s="1" t="s">
         <v>2414</v>
       </c>
     </row>
-    <row r="1102" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1102" spans="71:71">
       <c r="BS1102" s="1" t="s">
         <v>2415</v>
       </c>
     </row>
-    <row r="1103" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1103" spans="71:71">
       <c r="BS1103" s="1" t="s">
         <v>2416</v>
       </c>
     </row>
-    <row r="1104" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1104" spans="71:71">
       <c r="BS1104" s="1" t="s">
         <v>2417</v>
       </c>
     </row>
-    <row r="1105" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1105" spans="71:71">
       <c r="BS1105" s="1" t="s">
         <v>2418</v>
       </c>
     </row>
-    <row r="1106" spans="71:71" x14ac:dyDescent="0.35">
+    <row r="1106" spans="71:71">
       <c r="BS1106" s="1" t="s">
         <v>2419</v>
       </c>
@@ -18402,179 +18405,179 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{711972E5-7FA5-4D0C-9972-B416CFA60BFE}">
   <dimension ref="A1:CT226"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.4140625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.75" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="34.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="39.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="36.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="36.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="39.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="36.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.25" style="3" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="25" style="3" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="10.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="21.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="10.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="10.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="10.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="4.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="10.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="21.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="10.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="4.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.5" style="3" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="10" style="3" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="7.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="3.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="44" max="45" width="10.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="14.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="15.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="14.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="10.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="14.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="15.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="14.75" style="3" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="11.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="7.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="15.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="20.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="27.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="30.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="26.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="18.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="17.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="10.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="29.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="7.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="15.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="20.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="30.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="26.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="17.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="29.83203125" style="3" bestFit="1" customWidth="1"/>
     <col min="64" max="64" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="6.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="15.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="9.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="29.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="19.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="19.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="24.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="15.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="9.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="29.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="19.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="19.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="24.25" style="3" bestFit="1" customWidth="1"/>
     <col min="73" max="73" width="12" style="3" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="14.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="14.75" style="3" bestFit="1" customWidth="1"/>
     <col min="75" max="75" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="11.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="77" max="78" width="6.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="17.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="19.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="15.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="77" max="78" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="17.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="19.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="15.5" style="3" bestFit="1" customWidth="1"/>
     <col min="82" max="82" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="24.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="11.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="10.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="24.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="10.25" style="3" bestFit="1" customWidth="1"/>
     <col min="86" max="86" width="20" style="3" bestFit="1" customWidth="1"/>
     <col min="87" max="87" width="21" style="3" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="11.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="11.25" style="3" bestFit="1" customWidth="1"/>
     <col min="89" max="89" width="21" style="3" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="10.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="20.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="20.25" style="3" bestFit="1" customWidth="1"/>
     <col min="92" max="92" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="20.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="10.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="20.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="20.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="20.25" style="3" bestFit="1" customWidth="1"/>
     <col min="96" max="96" width="29" style="3" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="7.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="17.7265625" style="3" customWidth="1"/>
-    <col min="99" max="16384" width="11.453125" style="3"/>
+    <col min="97" max="97" width="7.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="17.75" style="3" customWidth="1"/>
+    <col min="99" max="16384" width="11.4140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="17">
       <c r="K1" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11">
       <c r="K2" s="5" t="s">
         <v>2424</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11">
       <c r="K3" s="5" t="s">
         <v>2426</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11">
       <c r="K4" s="5" t="s">
         <v>2427</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11">
       <c r="K5" s="5" t="s">
         <v>2428</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11">
       <c r="K6" s="5" t="s">
         <v>2425</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" s="22" t="s">
         <v>2515</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="26"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="22" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="23"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="28" t="s">
         <v>2516</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="23"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="29"/>
       <c r="D8" s="8" t="s">
         <v>2517</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="28" t="s">
         <v>2518</v>
       </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="22" t="s">
+      <c r="F8" s="29"/>
+      <c r="G8" s="28" t="s">
         <v>2519</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="22" t="s">
+      <c r="H8" s="29"/>
+      <c r="I8" s="28" t="s">
         <v>2517</v>
       </c>
-      <c r="J8" s="23"/>
+      <c r="J8" s="29"/>
       <c r="K8" s="8" t="s">
         <v>2478</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="22" t="s">
+    <row r="9" spans="1:11">
+      <c r="A9" s="28" t="s">
         <v>2520</v>
       </c>
-      <c r="B9" s="23"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="8" t="s">
         <v>2521</v>
       </c>
@@ -18593,19 +18596,19 @@
       <c r="H9" s="8" t="s">
         <v>2526</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="I9" s="28" t="s">
         <v>2527</v>
       </c>
-      <c r="J9" s="23"/>
+      <c r="J9" s="29"/>
       <c r="K9" s="8" t="s">
         <v>2528</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="24" t="s">
+    <row r="10" spans="1:11">
+      <c r="A10" s="22" t="s">
         <v>2542</v>
       </c>
-      <c r="B10" s="26"/>
+      <c r="B10" s="23"/>
       <c r="C10" s="18" t="s">
         <v>2543</v>
       </c>
@@ -18620,41 +18623,41 @@
       <c r="H10" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="J10" s="26"/>
+      <c r="J10" s="23"/>
       <c r="K10" s="18" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="24" t="s">
+    <row r="12" spans="1:11">
+      <c r="A12" s="22" t="s">
         <v>2529</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="26"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="22" t="s">
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="28" t="s">
         <v>2524</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="22" t="s">
+      <c r="B13" s="29"/>
+      <c r="C13" s="28" t="s">
         <v>2523</v>
       </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="22" t="s">
+      <c r="D13" s="29"/>
+      <c r="E13" s="28" t="s">
         <v>2530</v>
       </c>
-      <c r="F13" s="27"/>
-      <c r="G13" s="23"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F13" s="30"/>
+      <c r="G13" s="29"/>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="8" t="s">
         <v>2530</v>
       </c>
@@ -18677,7 +18680,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11">
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
       <c r="C15" s="20"/>
@@ -18686,123 +18689,123 @@
       <c r="F15" s="18"/>
       <c r="G15" s="19"/>
     </row>
-    <row r="17" spans="1:98" x14ac:dyDescent="0.35">
-      <c r="A17" s="28" t="s">
+    <row r="17" spans="1:98">
+      <c r="A17" s="24" t="s">
         <v>2535</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="29"/>
-      <c r="N17" s="29"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="28" t="s">
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="24" t="s">
         <v>2536</v>
       </c>
-      <c r="Q17" s="29"/>
-      <c r="R17" s="29"/>
-      <c r="S17" s="29"/>
-      <c r="T17" s="29"/>
-      <c r="U17" s="29"/>
-      <c r="V17" s="29"/>
-      <c r="W17" s="29"/>
-      <c r="X17" s="29"/>
-      <c r="Y17" s="29"/>
-      <c r="Z17" s="29"/>
-      <c r="AA17" s="29"/>
-      <c r="AB17" s="29"/>
-      <c r="AC17" s="29"/>
-      <c r="AD17" s="29"/>
-      <c r="AE17" s="29"/>
-      <c r="AF17" s="29"/>
-      <c r="AG17" s="29"/>
-      <c r="AH17" s="29"/>
-      <c r="AI17" s="29"/>
-      <c r="AJ17" s="29"/>
-      <c r="AK17" s="29"/>
-      <c r="AL17" s="29"/>
-      <c r="AM17" s="29"/>
-      <c r="AN17" s="29"/>
-      <c r="AO17" s="29"/>
-      <c r="AP17" s="29"/>
-      <c r="AQ17" s="29"/>
-      <c r="AR17" s="29"/>
-      <c r="AS17" s="29"/>
-      <c r="AT17" s="30"/>
-      <c r="AU17" s="28" t="s">
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="25"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
+      <c r="AH17" s="25"/>
+      <c r="AI17" s="25"/>
+      <c r="AJ17" s="25"/>
+      <c r="AK17" s="25"/>
+      <c r="AL17" s="25"/>
+      <c r="AM17" s="25"/>
+      <c r="AN17" s="25"/>
+      <c r="AO17" s="25"/>
+      <c r="AP17" s="25"/>
+      <c r="AQ17" s="25"/>
+      <c r="AR17" s="25"/>
+      <c r="AS17" s="25"/>
+      <c r="AT17" s="26"/>
+      <c r="AU17" s="24" t="s">
         <v>2537</v>
       </c>
-      <c r="AV17" s="29"/>
-      <c r="AW17" s="30"/>
-      <c r="AX17" s="28" t="s">
+      <c r="AV17" s="25"/>
+      <c r="AW17" s="26"/>
+      <c r="AX17" s="24" t="s">
         <v>2520</v>
       </c>
-      <c r="AY17" s="29"/>
-      <c r="AZ17" s="29"/>
-      <c r="BA17" s="29"/>
-      <c r="BB17" s="29"/>
-      <c r="BC17" s="29"/>
-      <c r="BD17" s="29"/>
-      <c r="BE17" s="29"/>
-      <c r="BF17" s="29"/>
-      <c r="BG17" s="29"/>
-      <c r="BH17" s="29"/>
-      <c r="BI17" s="29"/>
-      <c r="BJ17" s="30"/>
-      <c r="BK17" s="28" t="s">
+      <c r="AY17" s="25"/>
+      <c r="AZ17" s="25"/>
+      <c r="BA17" s="25"/>
+      <c r="BB17" s="25"/>
+      <c r="BC17" s="25"/>
+      <c r="BD17" s="25"/>
+      <c r="BE17" s="25"/>
+      <c r="BF17" s="25"/>
+      <c r="BG17" s="25"/>
+      <c r="BH17" s="25"/>
+      <c r="BI17" s="25"/>
+      <c r="BJ17" s="26"/>
+      <c r="BK17" s="24" t="s">
         <v>2521</v>
       </c>
-      <c r="BL17" s="29"/>
-      <c r="BM17" s="29"/>
-      <c r="BN17" s="29"/>
-      <c r="BO17" s="29"/>
-      <c r="BP17" s="29"/>
-      <c r="BQ17" s="29"/>
-      <c r="BR17" s="29"/>
-      <c r="BS17" s="29"/>
-      <c r="BT17" s="29"/>
-      <c r="BU17" s="30"/>
-      <c r="BV17" s="28" t="s">
+      <c r="BL17" s="25"/>
+      <c r="BM17" s="25"/>
+      <c r="BN17" s="25"/>
+      <c r="BO17" s="25"/>
+      <c r="BP17" s="25"/>
+      <c r="BQ17" s="25"/>
+      <c r="BR17" s="25"/>
+      <c r="BS17" s="25"/>
+      <c r="BT17" s="25"/>
+      <c r="BU17" s="26"/>
+      <c r="BV17" s="24" t="s">
         <v>2528</v>
       </c>
-      <c r="BW17" s="29"/>
-      <c r="BX17" s="29"/>
-      <c r="BY17" s="29"/>
-      <c r="BZ17" s="29"/>
-      <c r="CA17" s="29"/>
-      <c r="CB17" s="29"/>
-      <c r="CC17" s="30"/>
-      <c r="CD17" s="28" t="s">
+      <c r="BW17" s="25"/>
+      <c r="BX17" s="25"/>
+      <c r="BY17" s="25"/>
+      <c r="BZ17" s="25"/>
+      <c r="CA17" s="25"/>
+      <c r="CB17" s="25"/>
+      <c r="CC17" s="26"/>
+      <c r="CD17" s="24" t="s">
         <v>2538</v>
       </c>
-      <c r="CE17" s="29"/>
-      <c r="CF17" s="29"/>
-      <c r="CG17" s="29"/>
-      <c r="CH17" s="29"/>
-      <c r="CI17" s="29"/>
-      <c r="CJ17" s="29"/>
-      <c r="CK17" s="29"/>
-      <c r="CL17" s="29"/>
-      <c r="CM17" s="29"/>
-      <c r="CN17" s="29"/>
-      <c r="CO17" s="29"/>
-      <c r="CP17" s="29"/>
-      <c r="CQ17" s="29"/>
-      <c r="CR17" s="30"/>
-      <c r="CS17" s="28" t="s">
+      <c r="CE17" s="25"/>
+      <c r="CF17" s="25"/>
+      <c r="CG17" s="25"/>
+      <c r="CH17" s="25"/>
+      <c r="CI17" s="25"/>
+      <c r="CJ17" s="25"/>
+      <c r="CK17" s="25"/>
+      <c r="CL17" s="25"/>
+      <c r="CM17" s="25"/>
+      <c r="CN17" s="25"/>
+      <c r="CO17" s="25"/>
+      <c r="CP17" s="25"/>
+      <c r="CQ17" s="25"/>
+      <c r="CR17" s="26"/>
+      <c r="CS17" s="24" t="s">
         <v>2539</v>
       </c>
-      <c r="CT17" s="30"/>
-    </row>
-    <row r="18" spans="1:98" x14ac:dyDescent="0.35">
+      <c r="CT17" s="26"/>
+    </row>
+    <row r="18" spans="1:98">
       <c r="A18" s="6" t="s">
         <v>2429</v>
       </c>
@@ -19098,7 +19101,7 @@
         <v>2514</v>
       </c>
     </row>
-    <row r="19" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:98">
       <c r="A19" s="13"/>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -19202,7 +19205,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="20" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:98">
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -19295,7 +19298,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="21" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:98">
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -19388,7 +19391,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="22" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:98">
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -19481,7 +19484,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="23" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:98">
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -19574,7 +19577,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="24" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:98">
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
@@ -19667,7 +19670,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="25" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:98">
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
@@ -19760,7 +19763,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="26" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:98">
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -19853,7 +19856,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="27" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:98">
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -19946,7 +19949,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="28" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:98">
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -20039,7 +20042,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="29" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:98">
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -20132,7 +20135,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="30" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:98">
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -20225,7 +20228,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="31" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:98">
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
@@ -20318,7 +20321,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="32" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:98">
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -20411,7 +20414,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="33" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:98">
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
@@ -20504,7 +20507,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="34" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:98">
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -20597,7 +20600,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="35" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:98">
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
@@ -20690,7 +20693,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="36" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:98">
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -20783,7 +20786,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="37" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:98">
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -20876,7 +20879,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="38" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:98">
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -20969,7 +20972,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="39" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:98">
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
@@ -21062,7 +21065,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="40" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:98">
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -21155,7 +21158,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="41" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:98">
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
@@ -21248,7 +21251,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="42" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:98">
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
@@ -21341,7 +21344,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="43" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:98">
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -21434,7 +21437,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="44" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:98">
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
@@ -21527,7 +21530,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="45" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:98">
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
@@ -21620,7 +21623,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="46" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:98">
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
@@ -21713,7 +21716,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="47" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:98">
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
@@ -21806,7 +21809,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="48" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:98">
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
@@ -21899,7 +21902,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="49" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:98">
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
@@ -21992,7 +21995,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="50" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:98">
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
@@ -22085,7 +22088,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="51" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:98">
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
@@ -22178,7 +22181,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="52" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:98">
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
@@ -22271,7 +22274,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="53" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:98">
       <c r="B53" s="9"/>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
@@ -22364,7 +22367,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="54" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:98">
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
@@ -22457,7 +22460,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="55" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:98">
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
@@ -22550,7 +22553,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="56" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:98">
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
@@ -22643,7 +22646,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="57" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:98">
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
@@ -22736,7 +22739,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="58" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:98">
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
@@ -22829,7 +22832,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="59" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:98">
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
@@ -22922,7 +22925,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="60" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:98">
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
@@ -23015,7 +23018,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="61" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:98">
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
@@ -23108,7 +23111,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="62" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:98">
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
@@ -23201,7 +23204,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="63" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:98">
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
@@ -23294,7 +23297,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="64" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:98">
       <c r="B64" s="9"/>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
@@ -23387,7 +23390,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="65" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:98">
       <c r="B65" s="9"/>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
@@ -23480,7 +23483,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="66" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:98">
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
@@ -23573,7 +23576,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="67" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:98">
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
@@ -23666,7 +23669,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="68" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:98">
       <c r="B68" s="9"/>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
@@ -23759,7 +23762,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="69" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:98">
       <c r="B69" s="9"/>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
@@ -23852,7 +23855,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="70" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:98">
       <c r="B70" s="9"/>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
@@ -23945,7 +23948,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="71" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:98">
       <c r="B71" s="9"/>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
@@ -24038,7 +24041,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="72" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:98">
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
@@ -24131,7 +24134,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="73" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:98">
       <c r="B73" s="9"/>
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
@@ -24224,7 +24227,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="74" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:98">
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
@@ -24317,7 +24320,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="75" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:98">
       <c r="B75" s="9"/>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
@@ -24410,7 +24413,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="76" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:98">
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
@@ -24503,7 +24506,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="77" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:98">
       <c r="B77" s="9"/>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
@@ -24596,7 +24599,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="78" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:98">
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
@@ -24689,7 +24692,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="79" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:98">
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
@@ -24782,7 +24785,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="80" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:98">
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
@@ -24875,7 +24878,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="81" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:98">
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
@@ -24968,7 +24971,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="82" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:98">
       <c r="B82" s="9"/>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
@@ -25061,7 +25064,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="83" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:98">
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
@@ -25154,7 +25157,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="84" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:98">
       <c r="B84" s="9"/>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
@@ -25247,7 +25250,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="85" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:98">
       <c r="B85" s="9"/>
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
@@ -25340,7 +25343,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="86" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:98">
       <c r="B86" s="9"/>
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
@@ -25433,7 +25436,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="87" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:98">
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
@@ -25526,7 +25529,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="88" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:98">
       <c r="B88" s="9"/>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
@@ -25619,7 +25622,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="89" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:98">
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
@@ -25712,7 +25715,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="90" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:98">
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
@@ -25805,7 +25808,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="91" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:98">
       <c r="B91" s="9"/>
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
@@ -25898,7 +25901,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="92" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:98">
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
@@ -25991,7 +25994,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="93" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:98">
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
@@ -26084,7 +26087,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="94" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:98">
       <c r="B94" s="9"/>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
@@ -26177,7 +26180,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="95" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:98">
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
@@ -26270,7 +26273,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="96" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:98">
       <c r="B96" s="9"/>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
@@ -26363,7 +26366,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="97" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:98">
       <c r="B97" s="9"/>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
@@ -26456,7 +26459,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="98" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:98">
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
@@ -26549,7 +26552,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="99" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:98">
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
@@ -26642,7 +26645,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="100" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:98">
       <c r="B100" s="9"/>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
@@ -26735,7 +26738,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="101" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:98">
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
@@ -26828,7 +26831,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="102" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:98">
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
@@ -26921,7 +26924,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="103" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:98">
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
@@ -27014,7 +27017,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="104" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:98">
       <c r="B104" s="9"/>
       <c r="C104" s="9"/>
       <c r="D104" s="9"/>
@@ -27107,7 +27110,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="105" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:98">
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
       <c r="D105" s="9"/>
@@ -27200,7 +27203,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="106" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:98">
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
@@ -27293,7 +27296,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="107" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:98">
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
@@ -27386,7 +27389,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="108" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:98">
       <c r="B108" s="9"/>
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
@@ -27479,7 +27482,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="109" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:98">
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
@@ -27572,7 +27575,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="110" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:98">
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
@@ -27665,7 +27668,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="111" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:98">
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
@@ -27758,7 +27761,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="112" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:98">
       <c r="B112" s="9"/>
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
@@ -27851,7 +27854,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="113" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:98">
       <c r="B113" s="9"/>
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
@@ -27944,7 +27947,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="114" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:98">
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
@@ -28037,7 +28040,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="115" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:98">
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
@@ -28130,7 +28133,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="116" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:98">
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
@@ -28223,7 +28226,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="117" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:98">
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
@@ -28316,7 +28319,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="118" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:98">
       <c r="B118" s="9"/>
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
@@ -28409,7 +28412,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="119" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:98">
       <c r="B119" s="9"/>
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
@@ -28502,7 +28505,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="120" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:98">
       <c r="B120" s="9"/>
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
@@ -28595,7 +28598,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="121" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:98">
       <c r="B121" s="9"/>
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
@@ -28688,7 +28691,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="122" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:98">
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
@@ -28781,7 +28784,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="123" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:98">
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
@@ -28874,7 +28877,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="124" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:98">
       <c r="B124" s="9"/>
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
@@ -28967,7 +28970,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="125" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:98">
       <c r="B125" s="9"/>
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
@@ -29060,7 +29063,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="126" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:98">
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
@@ -29153,7 +29156,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="127" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:98">
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
@@ -29246,7 +29249,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="128" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:98">
       <c r="B128" s="9"/>
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
@@ -29339,7 +29342,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="129" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:98">
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
       <c r="D129" s="9"/>
@@ -29432,7 +29435,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="130" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:98">
       <c r="B130" s="9"/>
       <c r="C130" s="9"/>
       <c r="D130" s="9"/>
@@ -29525,7 +29528,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="131" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:98">
       <c r="B131" s="9"/>
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
@@ -29618,7 +29621,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="132" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:98">
       <c r="B132" s="9"/>
       <c r="C132" s="9"/>
       <c r="D132" s="9"/>
@@ -29711,7 +29714,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="133" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:98">
       <c r="B133" s="9"/>
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
@@ -29804,7 +29807,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="134" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:98">
       <c r="B134" s="9"/>
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
@@ -29897,7 +29900,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="135" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:98">
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
@@ -29990,7 +29993,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="136" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:98">
       <c r="B136" s="9"/>
       <c r="C136" s="9"/>
       <c r="D136" s="9"/>
@@ -30083,7 +30086,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="137" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:98">
       <c r="B137" s="9"/>
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
@@ -30176,7 +30179,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="138" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:98">
       <c r="B138" s="9"/>
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
@@ -30269,7 +30272,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="139" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:98">
       <c r="B139" s="9"/>
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
@@ -30362,7 +30365,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="140" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:98">
       <c r="B140" s="9"/>
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
@@ -30455,7 +30458,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="141" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:98">
       <c r="B141" s="9"/>
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
@@ -30548,7 +30551,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="142" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:98">
       <c r="B142" s="9"/>
       <c r="C142" s="9"/>
       <c r="D142" s="9"/>
@@ -30641,7 +30644,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="143" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:98">
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
       <c r="D143" s="9"/>
@@ -30734,7 +30737,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="144" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:98">
       <c r="B144" s="9"/>
       <c r="C144" s="9"/>
       <c r="D144" s="9"/>
@@ -30827,7 +30830,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="145" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="145" spans="2:98">
       <c r="B145" s="9"/>
       <c r="C145" s="9"/>
       <c r="D145" s="9"/>
@@ -30920,7 +30923,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="146" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:98">
       <c r="B146" s="9"/>
       <c r="C146" s="9"/>
       <c r="D146" s="9"/>
@@ -31013,7 +31016,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="147" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="147" spans="2:98">
       <c r="B147" s="9"/>
       <c r="C147" s="9"/>
       <c r="D147" s="9"/>
@@ -31106,7 +31109,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="148" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:98">
       <c r="B148" s="9"/>
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
@@ -31199,7 +31202,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="149" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:98">
       <c r="B149" s="9"/>
       <c r="C149" s="9"/>
       <c r="D149" s="9"/>
@@ -31292,7 +31295,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="150" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:98">
       <c r="B150" s="9"/>
       <c r="C150" s="9"/>
       <c r="D150" s="9"/>
@@ -31385,7 +31388,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="151" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="151" spans="2:98">
       <c r="B151" s="9"/>
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
@@ -31478,7 +31481,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="152" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="152" spans="2:98">
       <c r="B152" s="9"/>
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
@@ -31571,7 +31574,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="153" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="153" spans="2:98">
       <c r="B153" s="9"/>
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
@@ -31664,7 +31667,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="154" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="154" spans="2:98">
       <c r="B154" s="9"/>
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
@@ -31757,7 +31760,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="155" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="155" spans="2:98">
       <c r="B155" s="9"/>
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
@@ -31850,7 +31853,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="156" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="156" spans="2:98">
       <c r="B156" s="9"/>
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
@@ -31943,7 +31946,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="157" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:98">
       <c r="B157" s="9"/>
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
@@ -32036,7 +32039,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="158" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="158" spans="2:98">
       <c r="B158" s="9"/>
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
@@ -32129,7 +32132,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="159" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="159" spans="2:98">
       <c r="B159" s="9"/>
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
@@ -32222,7 +32225,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="160" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="160" spans="2:98">
       <c r="B160" s="9"/>
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
@@ -32315,7 +32318,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="161" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="161" spans="2:98">
       <c r="B161" s="9"/>
       <c r="C161" s="9"/>
       <c r="D161" s="9"/>
@@ -32408,7 +32411,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="162" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="162" spans="2:98">
       <c r="B162" s="9"/>
       <c r="C162" s="9"/>
       <c r="D162" s="9"/>
@@ -32501,7 +32504,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="163" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="163" spans="2:98">
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
@@ -32594,7 +32597,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="164" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="164" spans="2:98">
       <c r="B164" s="9"/>
       <c r="C164" s="9"/>
       <c r="D164" s="9"/>
@@ -32687,7 +32690,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="165" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="165" spans="2:98">
       <c r="B165" s="9"/>
       <c r="C165" s="9"/>
       <c r="D165" s="9"/>
@@ -32780,7 +32783,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="166" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="166" spans="2:98">
       <c r="B166" s="9"/>
       <c r="C166" s="9"/>
       <c r="D166" s="9"/>
@@ -32873,7 +32876,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="167" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="167" spans="2:98">
       <c r="B167" s="9"/>
       <c r="C167" s="9"/>
       <c r="D167" s="9"/>
@@ -32966,7 +32969,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="168" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="168" spans="2:98">
       <c r="B168" s="9"/>
       <c r="C168" s="9"/>
       <c r="D168" s="9"/>
@@ -33059,7 +33062,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="169" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="169" spans="2:98">
       <c r="B169" s="9"/>
       <c r="C169" s="9"/>
       <c r="D169" s="9"/>
@@ -33152,7 +33155,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="170" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="170" spans="2:98">
       <c r="B170" s="9"/>
       <c r="C170" s="9"/>
       <c r="D170" s="9"/>
@@ -33245,7 +33248,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="171" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="171" spans="2:98">
       <c r="B171" s="9"/>
       <c r="C171" s="9"/>
       <c r="D171" s="9"/>
@@ -33338,7 +33341,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="172" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="172" spans="2:98">
       <c r="B172" s="9"/>
       <c r="C172" s="9"/>
       <c r="D172" s="9"/>
@@ -33431,7 +33434,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="173" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="173" spans="2:98">
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
       <c r="D173" s="9"/>
@@ -33524,7 +33527,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="174" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="174" spans="2:98">
       <c r="B174" s="9"/>
       <c r="C174" s="9"/>
       <c r="D174" s="9"/>
@@ -33617,7 +33620,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="175" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="175" spans="2:98">
       <c r="B175" s="9"/>
       <c r="C175" s="9"/>
       <c r="D175" s="9"/>
@@ -33710,7 +33713,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="176" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="176" spans="2:98">
       <c r="B176" s="9"/>
       <c r="C176" s="9"/>
       <c r="D176" s="9"/>
@@ -33803,7 +33806,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="177" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="177" spans="2:98">
       <c r="B177" s="9"/>
       <c r="C177" s="9"/>
       <c r="D177" s="9"/>
@@ -33896,7 +33899,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="178" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="178" spans="2:98">
       <c r="B178" s="9"/>
       <c r="C178" s="9"/>
       <c r="D178" s="9"/>
@@ -33989,7 +33992,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="179" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="179" spans="2:98">
       <c r="B179" s="9"/>
       <c r="C179" s="9"/>
       <c r="D179" s="9"/>
@@ -34082,7 +34085,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="180" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="180" spans="2:98">
       <c r="B180" s="9"/>
       <c r="C180" s="9"/>
       <c r="D180" s="9"/>
@@ -34175,7 +34178,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="181" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="181" spans="2:98">
       <c r="B181" s="9"/>
       <c r="C181" s="9"/>
       <c r="D181" s="9"/>
@@ -34268,7 +34271,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="182" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="182" spans="2:98">
       <c r="B182" s="9"/>
       <c r="C182" s="9"/>
       <c r="D182" s="9"/>
@@ -34361,7 +34364,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="183" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="183" spans="2:98">
       <c r="B183" s="9"/>
       <c r="C183" s="9"/>
       <c r="D183" s="9"/>
@@ -34454,7 +34457,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="184" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="184" spans="2:98">
       <c r="B184" s="9"/>
       <c r="C184" s="9"/>
       <c r="D184" s="9"/>
@@ -34547,7 +34550,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="185" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="185" spans="2:98">
       <c r="B185" s="9"/>
       <c r="C185" s="9"/>
       <c r="D185" s="9"/>
@@ -34640,7 +34643,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="186" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:98">
       <c r="B186" s="9"/>
       <c r="C186" s="9"/>
       <c r="D186" s="9"/>
@@ -34733,7 +34736,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="187" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="187" spans="2:98">
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
       <c r="D187" s="9"/>
@@ -34826,7 +34829,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="188" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:98">
       <c r="B188" s="9"/>
       <c r="C188" s="9"/>
       <c r="D188" s="9"/>
@@ -34919,7 +34922,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="189" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:98">
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
       <c r="D189" s="9"/>
@@ -35012,7 +35015,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="190" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="190" spans="2:98">
       <c r="B190" s="9"/>
       <c r="C190" s="9"/>
       <c r="D190" s="9"/>
@@ -35105,7 +35108,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="191" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:98">
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
       <c r="D191" s="9"/>
@@ -35198,7 +35201,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="192" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="192" spans="2:98">
       <c r="B192" s="9"/>
       <c r="C192" s="9"/>
       <c r="D192" s="9"/>
@@ -35291,7 +35294,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="193" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="193" spans="2:98">
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
       <c r="D193" s="9"/>
@@ -35384,7 +35387,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="194" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:98">
       <c r="B194" s="9"/>
       <c r="C194" s="9"/>
       <c r="D194" s="9"/>
@@ -35477,7 +35480,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="195" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="195" spans="2:98">
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
       <c r="D195" s="9"/>
@@ -35570,7 +35573,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="196" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="196" spans="2:98">
       <c r="B196" s="9"/>
       <c r="C196" s="9"/>
       <c r="D196" s="9"/>
@@ -35663,7 +35666,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="197" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="197" spans="2:98">
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
       <c r="D197" s="9"/>
@@ -35756,7 +35759,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="198" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="198" spans="2:98">
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
       <c r="D198" s="9"/>
@@ -35849,7 +35852,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="199" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="199" spans="2:98">
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
       <c r="D199" s="9"/>
@@ -35942,7 +35945,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="200" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="200" spans="2:98">
       <c r="B200" s="9"/>
       <c r="C200" s="9"/>
       <c r="D200" s="9"/>
@@ -36035,7 +36038,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="201" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="201" spans="2:98">
       <c r="B201" s="9"/>
       <c r="C201" s="9"/>
       <c r="D201" s="9"/>
@@ -36128,7 +36131,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="202" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="202" spans="2:98">
       <c r="B202" s="9"/>
       <c r="C202" s="9"/>
       <c r="D202" s="9"/>
@@ -36221,7 +36224,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="203" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="203" spans="2:98">
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
       <c r="D203" s="9"/>
@@ -36314,7 +36317,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="204" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="204" spans="2:98">
       <c r="B204" s="9"/>
       <c r="C204" s="9"/>
       <c r="D204" s="9"/>
@@ -36407,7 +36410,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="205" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="205" spans="2:98">
       <c r="B205" s="9"/>
       <c r="C205" s="9"/>
       <c r="D205" s="9"/>
@@ -36500,7 +36503,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="206" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="206" spans="2:98">
       <c r="B206" s="9"/>
       <c r="C206" s="9"/>
       <c r="D206" s="9"/>
@@ -36593,7 +36596,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="207" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="207" spans="2:98">
       <c r="B207" s="9"/>
       <c r="C207" s="9"/>
       <c r="D207" s="9"/>
@@ -36686,7 +36689,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="208" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="208" spans="2:98">
       <c r="B208" s="9"/>
       <c r="C208" s="9"/>
       <c r="D208" s="9"/>
@@ -36779,7 +36782,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="209" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:98">
       <c r="B209" s="9"/>
       <c r="C209" s="9"/>
       <c r="D209" s="9"/>
@@ -36872,7 +36875,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="210" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="210" spans="2:98">
       <c r="B210" s="9"/>
       <c r="C210" s="9"/>
       <c r="D210" s="9"/>
@@ -36965,7 +36968,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="211" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="211" spans="2:98">
       <c r="B211" s="9"/>
       <c r="C211" s="9"/>
       <c r="D211" s="9"/>
@@ -37058,7 +37061,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="212" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="212" spans="2:98">
       <c r="B212" s="9"/>
       <c r="C212" s="9"/>
       <c r="D212" s="9"/>
@@ -37151,7 +37154,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="213" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="213" spans="2:98">
       <c r="B213" s="9"/>
       <c r="C213" s="9"/>
       <c r="D213" s="9"/>
@@ -37244,7 +37247,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="214" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="214" spans="2:98">
       <c r="B214" s="9"/>
       <c r="C214" s="9"/>
       <c r="D214" s="9"/>
@@ -37337,7 +37340,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="215" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="215" spans="2:98">
       <c r="B215" s="9"/>
       <c r="C215" s="9"/>
       <c r="D215" s="9"/>
@@ -37430,7 +37433,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="216" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="216" spans="2:98">
       <c r="B216" s="9"/>
       <c r="C216" s="9"/>
       <c r="D216" s="9"/>
@@ -37523,7 +37526,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="217" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="217" spans="2:98">
       <c r="B217" s="9"/>
       <c r="C217" s="9"/>
       <c r="D217" s="9"/>
@@ -37616,7 +37619,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="218" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="218" spans="2:98">
       <c r="B218" s="9"/>
       <c r="C218" s="9"/>
       <c r="D218" s="9"/>
@@ -37709,7 +37712,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="219" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="219" spans="2:98">
       <c r="B219" s="9"/>
       <c r="C219" s="9"/>
       <c r="D219" s="9"/>
@@ -37802,7 +37805,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="220" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="220" spans="2:98">
       <c r="B220" s="9"/>
       <c r="C220" s="9"/>
       <c r="D220" s="9"/>
@@ -37895,7 +37898,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="221" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="221" spans="2:98">
       <c r="B221" s="9"/>
       <c r="C221" s="9"/>
       <c r="D221" s="9"/>
@@ -37988,7 +37991,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="222" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="222" spans="2:98">
       <c r="B222" s="9"/>
       <c r="C222" s="9"/>
       <c r="D222" s="9"/>
@@ -38081,7 +38084,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="223" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="223" spans="2:98">
       <c r="B223" s="9"/>
       <c r="C223" s="9"/>
       <c r="D223" s="9"/>
@@ -38174,7 +38177,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="224" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="224" spans="2:98">
       <c r="B224" s="9"/>
       <c r="C224" s="9"/>
       <c r="D224" s="9"/>
@@ -38267,7 +38270,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="225" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="225" spans="2:98">
       <c r="B225" s="9"/>
       <c r="C225" s="9"/>
       <c r="D225" s="9"/>
@@ -38360,7 +38363,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="226" spans="2:98" x14ac:dyDescent="0.35">
+    <row r="226" spans="2:98">
       <c r="B226" s="9"/>
       <c r="C226" s="9"/>
       <c r="D226" s="9"/>
@@ -38449,11 +38452,13 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="AU17:AW17"/>
-    <mergeCell ref="AX17:BJ17"/>
-    <mergeCell ref="BK17:BU17"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
     <mergeCell ref="BV17:CC17"/>
     <mergeCell ref="CD17:CR17"/>
     <mergeCell ref="CS17:CT17"/>
@@ -38463,13 +38468,11 @@
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="A17:O17"/>
     <mergeCell ref="P17:AT17"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="AU17:AW17"/>
+    <mergeCell ref="AX17:BJ17"/>
+    <mergeCell ref="BK17:BU17"/>
   </mergeCells>
   <dataValidations xWindow="1438" yWindow="402" count="54">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Tipo identificación Inválido" error="El tipo de identificación del empleado introducido no es válido." promptTitle="Tipo identificación" prompt="Elija el tipo de identificación del empleado." sqref="B19:B226 CS19:CS225" xr:uid="{20D274F8-44C7-42B5-AB12-5C0ED94BF9C3}">
